--- a/data/macro/Europe/CPI.xlsx
+++ b/data/macro/Europe/CPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\Europe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA13121-482B-4288-A74B-1032BAE7191E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E071F1A6-49A6-4964-A3E0-7CE244686190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPICEMU" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Release Date</t>
   </si>
@@ -66,15 +66,19 @@
     <t>monthly</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Preliminary Release</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -151,15 +155,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -168,17 +172,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="1" builtinId="5"/>
@@ -461,20 +471,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G640"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H642"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.09765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
@@ -496,21 +506,30 @@
       <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="5">
         <v>33270</v>
       </c>
+      <c r="C2" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E2" s="3">
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="5">
         <v>33298</v>
       </c>
+      <c r="C3" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E3" s="3">
         <v>4.1000000000000002E-2</v>
       </c>
@@ -518,11 +537,14 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="5">
         <v>33329</v>
       </c>
+      <c r="C4" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E4" s="3">
         <v>3.9E-2</v>
       </c>
@@ -530,11 +552,14 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="5">
         <v>33359</v>
       </c>
+      <c r="C5" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E5" s="3">
         <v>3.9E-2</v>
       </c>
@@ -542,11 +567,14 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="5">
         <v>33390</v>
       </c>
+      <c r="C6" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E6" s="3">
         <v>4.1000000000000002E-2</v>
       </c>
@@ -554,11 +582,14 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="5">
         <v>33420</v>
       </c>
+      <c r="C7" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E7" s="3">
         <v>4.2999999999999997E-2</v>
       </c>
@@ -566,11 +597,14 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="5">
         <v>33451</v>
       </c>
+      <c r="C8" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E8" s="3">
         <v>0.05</v>
       </c>
@@ -578,11 +612,14 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="5">
         <v>33482</v>
       </c>
+      <c r="C9" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E9" s="3">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -590,11 +627,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="5">
         <v>33512</v>
       </c>
+      <c r="C10" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E10" s="3">
         <v>3.9E-2</v>
       </c>
@@ -602,11 +642,14 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="5">
         <v>33543</v>
       </c>
+      <c r="C11" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E11" s="3">
         <v>3.6999999999999998E-2</v>
       </c>
@@ -614,11 +657,14 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="5">
         <v>33573</v>
       </c>
+      <c r="C12" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E12" s="3">
         <v>4.1000000000000002E-2</v>
       </c>
@@ -626,11 +672,14 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="5">
         <v>33604</v>
       </c>
+      <c r="C13" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E13" s="3">
         <v>4.1000000000000002E-2</v>
       </c>
@@ -638,11 +687,14 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="5">
         <v>33635</v>
       </c>
+      <c r="C14" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E14" s="3">
         <v>3.9E-2</v>
       </c>
@@ -650,11 +702,14 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="5">
         <v>33664</v>
       </c>
+      <c r="C15" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E15" s="3">
         <v>3.7999999999999999E-2</v>
       </c>
@@ -662,10 +717,13 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="5">
         <v>33695</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0.45833333333333331</v>
       </c>
       <c r="E16" s="3">
         <v>4.2999999999999997E-2</v>
@@ -679,6 +737,9 @@
       <c r="B17" s="5">
         <v>33725</v>
       </c>
+      <c r="C17" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E17" s="3">
         <v>4.2000000000000003E-2</v>
       </c>
@@ -691,6 +752,9 @@
       <c r="B18" s="5">
         <v>33756</v>
       </c>
+      <c r="C18" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E18" s="3">
         <v>0.04</v>
       </c>
@@ -703,6 +767,9 @@
       <c r="B19" s="5">
         <v>33786</v>
       </c>
+      <c r="C19" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E19" s="3">
         <v>3.9E-2</v>
       </c>
@@ -715,6 +782,9 @@
       <c r="B20" s="5">
         <v>33817</v>
       </c>
+      <c r="C20" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E20" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -727,6 +797,9 @@
       <c r="B21" s="5">
         <v>33848</v>
       </c>
+      <c r="C21" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E21" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -739,6 +812,9 @@
       <c r="B22" s="5">
         <v>33878</v>
       </c>
+      <c r="C22" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E22" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -751,6 +827,9 @@
       <c r="B23" s="5">
         <v>33909</v>
       </c>
+      <c r="C23" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E23" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -763,6 +842,9 @@
       <c r="B24" s="5">
         <v>33939</v>
       </c>
+      <c r="C24" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E24" s="3">
         <v>3.1E-2</v>
       </c>
@@ -775,6 +857,9 @@
       <c r="B25" s="5">
         <v>33970</v>
       </c>
+      <c r="C25" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E25" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -787,6 +872,9 @@
       <c r="B26" s="5">
         <v>34001</v>
       </c>
+      <c r="C26" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E26" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
@@ -799,6 +887,9 @@
       <c r="B27" s="5">
         <v>34029</v>
       </c>
+      <c r="C27" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E27" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
@@ -811,6 +902,9 @@
       <c r="B28" s="5">
         <v>34060</v>
       </c>
+      <c r="C28" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E28" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -823,6 +917,9 @@
       <c r="B29" s="5">
         <v>34090</v>
       </c>
+      <c r="C29" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E29" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -835,6 +932,9 @@
       <c r="B30" s="5">
         <v>34121</v>
       </c>
+      <c r="C30" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E30" s="3">
         <v>3.1E-2</v>
       </c>
@@ -847,6 +947,9 @@
       <c r="B31" s="5">
         <v>34151</v>
       </c>
+      <c r="C31" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E31" s="3">
         <v>3.1E-2</v>
       </c>
@@ -859,6 +962,9 @@
       <c r="B32" s="5">
         <v>34182</v>
       </c>
+      <c r="C32" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E32" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -871,6 +977,9 @@
       <c r="B33" s="5">
         <v>34213</v>
       </c>
+      <c r="C33" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E33" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -883,6 +992,9 @@
       <c r="B34" s="5">
         <v>34243</v>
       </c>
+      <c r="C34" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E34" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -895,6 +1007,9 @@
       <c r="B35" s="5">
         <v>34274</v>
       </c>
+      <c r="C35" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E35" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -907,6 +1022,9 @@
       <c r="B36" s="5">
         <v>34304</v>
       </c>
+      <c r="C36" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E36" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -919,6 +1037,9 @@
       <c r="B37" s="5">
         <v>34335</v>
       </c>
+      <c r="C37" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E37" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -931,6 +1052,9 @@
       <c r="B38" s="5">
         <v>34366</v>
       </c>
+      <c r="C38" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E38" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -943,6 +1067,9 @@
       <c r="B39" s="5">
         <v>34394</v>
       </c>
+      <c r="C39" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E39" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -955,6 +1082,9 @@
       <c r="B40" s="5">
         <v>34425</v>
       </c>
+      <c r="C40" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E40" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -967,6 +1097,9 @@
       <c r="B41" s="5">
         <v>34455</v>
       </c>
+      <c r="C41" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E41" s="3">
         <v>2.7E-2</v>
       </c>
@@ -979,6 +1112,9 @@
       <c r="B42" s="5">
         <v>34486</v>
       </c>
+      <c r="C42" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E42" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -991,6 +1127,9 @@
       <c r="B43" s="5">
         <v>34516</v>
       </c>
+      <c r="C43" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E43" s="3">
         <v>2.7E-2</v>
       </c>
@@ -1003,6 +1142,9 @@
       <c r="B44" s="5">
         <v>34547</v>
       </c>
+      <c r="C44" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E44" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -1015,6 +1157,9 @@
       <c r="B45" s="5">
         <v>34578</v>
       </c>
+      <c r="C45" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E45" s="3">
         <v>2.7E-2</v>
       </c>
@@ -1027,6 +1172,9 @@
       <c r="B46" s="5">
         <v>34608</v>
       </c>
+      <c r="C46" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E46" s="3">
         <v>2.7E-2</v>
       </c>
@@ -1039,6 +1187,9 @@
       <c r="B47" s="5">
         <v>34639</v>
       </c>
+      <c r="C47" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E47" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -1051,6 +1202,9 @@
       <c r="B48" s="5">
         <v>34669</v>
       </c>
+      <c r="C48" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E48" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1063,6 +1217,9 @@
       <c r="B49" s="5">
         <v>34700</v>
       </c>
+      <c r="C49" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E49" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -1075,6 +1232,9 @@
       <c r="B50" s="5">
         <v>34731</v>
       </c>
+      <c r="C50" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E50" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1087,6 +1247,9 @@
       <c r="B51" s="5">
         <v>34759</v>
       </c>
+      <c r="C51" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E51" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1099,6 +1262,9 @@
       <c r="B52" s="5">
         <v>34790</v>
       </c>
+      <c r="C52" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E52" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -1111,6 +1277,9 @@
       <c r="B53" s="5">
         <v>34820</v>
       </c>
+      <c r="C53" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E53" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -1123,6 +1292,9 @@
       <c r="B54" s="5">
         <v>34851</v>
       </c>
+      <c r="C54" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E54" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1135,6 +1307,9 @@
       <c r="B55" s="5">
         <v>34881</v>
       </c>
+      <c r="C55" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E55" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -1147,6 +1322,9 @@
       <c r="B56" s="5">
         <v>34912</v>
       </c>
+      <c r="C56" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E56" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1159,6 +1337,9 @@
       <c r="B57" s="5">
         <v>34943</v>
       </c>
+      <c r="C57" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E57" s="3">
         <v>2.3E-2</v>
       </c>
@@ -1171,6 +1352,9 @@
       <c r="B58" s="5">
         <v>34973</v>
       </c>
+      <c r="C58" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E58" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1183,6 +1367,9 @@
       <c r="B59" s="5">
         <v>35004</v>
       </c>
+      <c r="C59" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E59" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1195,6 +1382,9 @@
       <c r="B60" s="5">
         <v>35034</v>
       </c>
+      <c r="C60" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E60" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1207,6 +1397,9 @@
       <c r="B61" s="5">
         <v>35065</v>
       </c>
+      <c r="C61" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E61" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1219,6 +1412,9 @@
       <c r="B62" s="5">
         <v>35096</v>
       </c>
+      <c r="C62" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E62" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1231,6 +1427,9 @@
       <c r="B63" s="5">
         <v>35125</v>
       </c>
+      <c r="C63" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E63" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1243,6 +1442,9 @@
       <c r="B64" s="5">
         <v>35156</v>
       </c>
+      <c r="C64" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E64" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1255,6 +1457,9 @@
       <c r="B65" s="5">
         <v>35186</v>
       </c>
+      <c r="C65" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E65" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1267,6 +1472,9 @@
       <c r="B66" s="5">
         <v>35217</v>
       </c>
+      <c r="C66" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E66" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -1279,6 +1487,9 @@
       <c r="B67" s="5">
         <v>35247</v>
       </c>
+      <c r="C67" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E67" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -1291,6 +1502,9 @@
       <c r="B68" s="5">
         <v>35278</v>
       </c>
+      <c r="C68" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E68" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -1303,6 +1517,9 @@
       <c r="B69" s="5">
         <v>35309</v>
       </c>
+      <c r="C69" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E69" s="3">
         <v>0.02</v>
       </c>
@@ -1315,6 +1532,9 @@
       <c r="B70" s="5">
         <v>35339</v>
       </c>
+      <c r="C70" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E70" s="3">
         <v>0.02</v>
       </c>
@@ -1327,6 +1547,9 @@
       <c r="B71" s="5">
         <v>35370</v>
       </c>
+      <c r="C71" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E71" s="3">
         <v>0.02</v>
       </c>
@@ -1339,6 +1562,9 @@
       <c r="B72" s="5">
         <v>35400</v>
       </c>
+      <c r="C72" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E72" s="3">
         <v>1.9E-2</v>
       </c>
@@ -1351,6 +1577,9 @@
       <c r="B73" s="5">
         <v>35431</v>
       </c>
+      <c r="C73" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E73" s="3">
         <v>1.9E-2</v>
       </c>
@@ -1363,6 +1592,9 @@
       <c r="B74" s="5">
         <v>35462</v>
       </c>
+      <c r="C74" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E74" s="3">
         <v>0.02</v>
       </c>
@@ -1375,6 +1607,9 @@
       <c r="B75" s="5">
         <v>35490</v>
       </c>
+      <c r="C75" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E75" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -1387,6 +1622,9 @@
       <c r="B76" s="5">
         <v>35521</v>
       </c>
+      <c r="C76" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E76" s="3">
         <v>1.6E-2</v>
       </c>
@@ -1399,6 +1637,9 @@
       <c r="B77" s="5">
         <v>35551</v>
       </c>
+      <c r="C77" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E77" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -1411,6 +1652,9 @@
       <c r="B78" s="5">
         <v>35582</v>
       </c>
+      <c r="C78" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E78" s="3">
         <v>1.4E-2</v>
       </c>
@@ -1423,6 +1667,9 @@
       <c r="B79" s="5">
         <v>35612</v>
       </c>
+      <c r="C79" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E79" s="3">
         <v>1.4E-2</v>
       </c>
@@ -1435,6 +1682,9 @@
       <c r="B80" s="5">
         <v>35643</v>
       </c>
+      <c r="C80" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E80" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -1447,6 +1697,9 @@
       <c r="B81" s="5">
         <v>35674</v>
       </c>
+      <c r="C81" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E81" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -1459,6 +1712,9 @@
       <c r="B82" s="5">
         <v>35704</v>
       </c>
+      <c r="C82" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E82" s="3">
         <v>1.6E-2</v>
       </c>
@@ -1471,6 +1727,9 @@
       <c r="B83" s="5">
         <v>35735</v>
       </c>
+      <c r="C83" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E83" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -1483,6 +1742,9 @@
       <c r="B84" s="5">
         <v>35765</v>
       </c>
+      <c r="C84" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E84" s="3">
         <v>1.6E-2</v>
       </c>
@@ -1495,6 +1757,9 @@
       <c r="B85" s="5">
         <v>35796</v>
       </c>
+      <c r="C85" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E85" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -1507,6 +1772,9 @@
       <c r="B86" s="5">
         <v>35827</v>
       </c>
+      <c r="C86" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E86" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -1519,6 +1787,9 @@
       <c r="B87" s="5">
         <v>35855</v>
       </c>
+      <c r="C87" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E87" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -1531,6 +1802,9 @@
       <c r="B88" s="5">
         <v>35886</v>
       </c>
+      <c r="C88" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E88" s="3">
         <v>1.2E-2</v>
       </c>
@@ -1543,6 +1817,9 @@
       <c r="B89" s="5">
         <v>35916</v>
       </c>
+      <c r="C89" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E89" s="3">
         <v>1.4E-2</v>
       </c>
@@ -1555,6 +1832,9 @@
       <c r="B90" s="5">
         <v>35947</v>
       </c>
+      <c r="C90" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E90" s="3">
         <v>1.4E-2</v>
       </c>
@@ -1567,6 +1847,9 @@
       <c r="B91" s="5">
         <v>35977</v>
       </c>
+      <c r="C91" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E91" s="3">
         <v>1.4E-2</v>
       </c>
@@ -1579,6 +1862,9 @@
       <c r="B92" s="5">
         <v>36008</v>
       </c>
+      <c r="C92" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E92" s="3">
         <v>1.4E-2</v>
       </c>
@@ -1591,6 +1877,9 @@
       <c r="B93" s="5">
         <v>36039</v>
       </c>
+      <c r="C93" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E93" s="3">
         <v>1.2E-2</v>
       </c>
@@ -1603,6 +1892,9 @@
       <c r="B94" s="5">
         <v>36069</v>
       </c>
+      <c r="C94" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E94" s="3">
         <v>0.01</v>
       </c>
@@ -1615,6 +1907,9 @@
       <c r="B95" s="5">
         <v>36100</v>
       </c>
+      <c r="C95" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E95" s="3">
         <v>0.01</v>
       </c>
@@ -1627,6 +1922,9 @@
       <c r="B96" s="5">
         <v>36130</v>
       </c>
+      <c r="C96" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E96" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -1639,6 +1937,9 @@
       <c r="B97" s="5">
         <v>36161</v>
       </c>
+      <c r="C97" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E97" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -1651,6 +1952,9 @@
       <c r="B98" s="5">
         <v>36192</v>
       </c>
+      <c r="C98" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E98" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -1663,6 +1967,9 @@
       <c r="B99" s="5">
         <v>36220</v>
       </c>
+      <c r="C99" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E99" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -1675,6 +1982,9 @@
       <c r="B100" s="5">
         <v>36251</v>
       </c>
+      <c r="C100" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E100" s="3">
         <v>0.01</v>
       </c>
@@ -1687,6 +1997,9 @@
       <c r="B101" s="5">
         <v>36281</v>
       </c>
+      <c r="C101" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E101" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -1699,6 +2012,9 @@
       <c r="B102" s="5">
         <v>36312</v>
       </c>
+      <c r="C102" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E102" s="3">
         <v>0.01</v>
       </c>
@@ -1711,6 +2027,9 @@
       <c r="B103" s="5">
         <v>36342</v>
       </c>
+      <c r="C103" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E103" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -1723,6 +2042,9 @@
       <c r="B104" s="5">
         <v>36373</v>
       </c>
+      <c r="C104" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E104" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -1735,6 +2057,9 @@
       <c r="B105" s="5">
         <v>36404</v>
       </c>
+      <c r="C105" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E105" s="3">
         <v>1.2E-2</v>
       </c>
@@ -1747,6 +2072,9 @@
       <c r="B106" s="5">
         <v>36434</v>
       </c>
+      <c r="C106" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E106" s="3">
         <v>1.2E-2</v>
       </c>
@@ -1759,6 +2087,9 @@
       <c r="B107" s="5">
         <v>36465</v>
       </c>
+      <c r="C107" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E107" s="3">
         <v>1.4E-2</v>
       </c>
@@ -1771,6 +2102,9 @@
       <c r="B108" s="5">
         <v>36495</v>
       </c>
+      <c r="C108" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E108" s="3">
         <v>1.6E-2</v>
       </c>
@@ -1783,6 +2117,9 @@
       <c r="B109" s="5">
         <v>36526</v>
       </c>
+      <c r="C109" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E109" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -1795,6 +2132,9 @@
       <c r="B110" s="5">
         <v>36557</v>
       </c>
+      <c r="C110" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E110" s="3">
         <v>0.02</v>
       </c>
@@ -1807,6 +2147,9 @@
       <c r="B111" s="5">
         <v>36586</v>
       </c>
+      <c r="C111" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E111" s="3">
         <v>0.02</v>
       </c>
@@ -1819,6 +2162,9 @@
       <c r="B112" s="5">
         <v>36617</v>
       </c>
+      <c r="C112" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E112" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -1831,6 +2177,9 @@
       <c r="B113" s="5">
         <v>36647</v>
       </c>
+      <c r="C113" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E113" s="3">
         <v>1.9E-2</v>
       </c>
@@ -1843,6 +2192,9 @@
       <c r="B114" s="5">
         <v>36678</v>
       </c>
+      <c r="C114" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E114" s="3">
         <v>1.9E-2</v>
       </c>
@@ -1855,6 +2207,9 @@
       <c r="B115" s="5">
         <v>36708</v>
       </c>
+      <c r="C115" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E115" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1867,6 +2222,9 @@
       <c r="B116" s="5">
         <v>36739</v>
       </c>
+      <c r="C116" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E116" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1879,6 +2237,9 @@
       <c r="B117" s="5">
         <v>36770</v>
       </c>
+      <c r="C117" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E117" s="3">
         <v>2.3E-2</v>
       </c>
@@ -1891,6 +2252,9 @@
       <c r="B118" s="5">
         <v>36800</v>
       </c>
+      <c r="C118" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E118" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -1903,6 +2267,9 @@
       <c r="B119" s="5">
         <v>36831</v>
       </c>
+      <c r="C119" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E119" s="3">
         <v>2.7E-2</v>
       </c>
@@ -1915,6 +2282,9 @@
       <c r="B120" s="5">
         <v>36861</v>
       </c>
+      <c r="C120" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E120" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -1927,6 +2297,9 @@
       <c r="B121" s="5">
         <v>36892</v>
       </c>
+      <c r="C121" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E121" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -1939,6 +2312,9 @@
       <c r="B122" s="5">
         <v>36923</v>
       </c>
+      <c r="C122" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E122" s="3">
         <v>2.4E-2</v>
       </c>
@@ -1951,6 +2327,9 @@
       <c r="B123" s="5">
         <v>36951</v>
       </c>
+      <c r="C123" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E123" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -1963,6 +2342,9 @@
       <c r="B124" s="5">
         <v>36982</v>
       </c>
+      <c r="C124" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E124" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -1975,6 +2357,9 @@
       <c r="B125" s="5">
         <v>37012</v>
       </c>
+      <c r="C125" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E125" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -1987,6 +2372,9 @@
       <c r="B126" s="5">
         <v>37043</v>
       </c>
+      <c r="C126" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E126" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
@@ -1999,6 +2387,9 @@
       <c r="B127" s="5">
         <v>37073</v>
       </c>
+      <c r="C127" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E127" s="3">
         <v>0.03</v>
       </c>
@@ -2011,6 +2402,9 @@
       <c r="B128" s="5">
         <v>37104</v>
       </c>
+      <c r="C128" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E128" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -2023,6 +2417,9 @@
       <c r="B129" s="5">
         <v>37135</v>
       </c>
+      <c r="C129" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E129" s="3">
         <v>2.7E-2</v>
       </c>
@@ -2035,6 +2432,9 @@
       <c r="B130" s="5">
         <v>37165</v>
       </c>
+      <c r="C130" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E130" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2047,6 +2447,9 @@
       <c r="B131" s="5">
         <v>37196</v>
       </c>
+      <c r="C131" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E131" s="3">
         <v>2.4E-2</v>
       </c>
@@ -2059,6 +2462,9 @@
       <c r="B132" s="5">
         <v>37226</v>
       </c>
+      <c r="C132" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E132" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2071,6 +2477,9 @@
       <c r="B133" s="5">
         <v>37257</v>
       </c>
+      <c r="C133" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E133" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2083,6 +2492,9 @@
       <c r="B134" s="5">
         <v>37288</v>
       </c>
+      <c r="C134" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E134" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2095,6 +2507,9 @@
       <c r="B135" s="5">
         <v>37316</v>
       </c>
+      <c r="C135" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E135" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2107,6 +2522,9 @@
       <c r="B136" s="5">
         <v>37347</v>
       </c>
+      <c r="C136" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E136" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2119,6 +2537,9 @@
       <c r="B137" s="5">
         <v>37377</v>
       </c>
+      <c r="C137" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E137" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2131,6 +2552,9 @@
       <c r="B138" s="5">
         <v>37408</v>
       </c>
+      <c r="C138" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E138" s="3">
         <v>0.02</v>
       </c>
@@ -2143,6 +2567,9 @@
       <c r="B139" s="5">
         <v>37438</v>
       </c>
+      <c r="C139" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E139" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -2155,6 +2582,9 @@
       <c r="B140" s="5">
         <v>37469</v>
       </c>
+      <c r="C140" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E140" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2167,6 +2597,9 @@
       <c r="B141" s="5">
         <v>37500</v>
       </c>
+      <c r="C141" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E141" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2179,6 +2612,9 @@
       <c r="B142" s="5">
         <v>37530</v>
       </c>
+      <c r="C142" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E142" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2191,6 +2627,9 @@
       <c r="B143" s="5">
         <v>37561</v>
       </c>
+      <c r="C143" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E143" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2203,6 +2642,9 @@
       <c r="B144" s="5">
         <v>37591</v>
       </c>
+      <c r="C144" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E144" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2215,6 +2657,9 @@
       <c r="B145" s="5">
         <v>37622</v>
       </c>
+      <c r="C145" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E145" s="3">
         <v>2.3E-2</v>
       </c>
@@ -2227,6 +2672,9 @@
       <c r="B146" s="5">
         <v>37653</v>
       </c>
+      <c r="C146" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E146" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2239,6 +2687,9 @@
       <c r="B147" s="5">
         <v>37681</v>
       </c>
+      <c r="C147" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E147" s="3">
         <v>2.3E-2</v>
       </c>
@@ -2251,6 +2702,9 @@
       <c r="B148" s="5">
         <v>37712</v>
       </c>
+      <c r="C148" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E148" s="3">
         <v>2.4E-2</v>
       </c>
@@ -2263,6 +2717,9 @@
       <c r="B149" s="5">
         <v>37742</v>
       </c>
+      <c r="C149" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E149" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2275,6 +2732,9 @@
       <c r="B150" s="5">
         <v>37773</v>
       </c>
+      <c r="C150" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E150" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2287,6 +2747,9 @@
       <c r="B151" s="5">
         <v>37803</v>
       </c>
+      <c r="C151" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E151" s="3">
         <v>0.02</v>
       </c>
@@ -2299,6 +2762,9 @@
       <c r="B152" s="5">
         <v>37834</v>
       </c>
+      <c r="C152" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E152" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2311,6 +2777,9 @@
       <c r="B153" s="5">
         <v>37865</v>
       </c>
+      <c r="C153" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E153" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2323,6 +2792,9 @@
       <c r="B154" s="5">
         <v>37895</v>
       </c>
+      <c r="C154" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E154" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2335,6 +2807,9 @@
       <c r="B155" s="5">
         <v>37926</v>
       </c>
+      <c r="C155" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E155" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2347,6 +2822,9 @@
       <c r="B156" s="5">
         <v>37956</v>
       </c>
+      <c r="C156" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E156" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2359,6 +2837,9 @@
       <c r="B157" s="5">
         <v>37987</v>
       </c>
+      <c r="C157" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E157" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2371,6 +2852,9 @@
       <c r="B158" s="5">
         <v>38018</v>
       </c>
+      <c r="C158" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E158" s="3">
         <v>0.02</v>
       </c>
@@ -2383,6 +2867,9 @@
       <c r="B159" s="5">
         <v>38047</v>
       </c>
+      <c r="C159" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E159" s="3">
         <v>1.6E-2</v>
       </c>
@@ -2395,6 +2882,9 @@
       <c r="B160" s="5">
         <v>38078</v>
       </c>
+      <c r="C160" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E160" s="3">
         <v>1.6E-2</v>
       </c>
@@ -2407,6 +2897,9 @@
       <c r="B161" s="5">
         <v>38108</v>
       </c>
+      <c r="C161" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E161" s="3">
         <v>0.02</v>
       </c>
@@ -2419,6 +2912,9 @@
       <c r="B162" s="5">
         <v>38139</v>
       </c>
+      <c r="C162" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E162" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2431,6 +2927,9 @@
       <c r="B163" s="5">
         <v>38169</v>
       </c>
+      <c r="C163" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E163" s="3">
         <v>2.4E-2</v>
       </c>
@@ -2443,6 +2942,9 @@
       <c r="B164" s="5">
         <v>38200</v>
       </c>
+      <c r="C164" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E164" s="3">
         <v>2.4E-2</v>
       </c>
@@ -2455,6 +2957,9 @@
       <c r="B165" s="5">
         <v>38231</v>
       </c>
+      <c r="C165" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E165" s="3">
         <v>2.3E-2</v>
       </c>
@@ -2467,6 +2972,9 @@
       <c r="B166" s="5">
         <v>38261</v>
       </c>
+      <c r="C166" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E166" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2479,6 +2987,9 @@
       <c r="B167" s="5">
         <v>38292</v>
       </c>
+      <c r="C167" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E167" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2491,6 +3002,9 @@
       <c r="B168" s="5">
         <v>38322</v>
       </c>
+      <c r="C168" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E168" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2503,6 +3017,9 @@
       <c r="B169" s="5">
         <v>38353</v>
       </c>
+      <c r="C169" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E169" s="3">
         <v>2.3E-2</v>
       </c>
@@ -2515,6 +3032,9 @@
       <c r="B170" s="5">
         <v>38384</v>
       </c>
+      <c r="C170" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E170" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2527,6 +3047,9 @@
       <c r="B171" s="5">
         <v>38412</v>
       </c>
+      <c r="C171" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E171" s="3">
         <v>0.02</v>
       </c>
@@ -2539,6 +3062,9 @@
       <c r="B172" s="5">
         <v>38443</v>
       </c>
+      <c r="C172" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E172" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2551,6 +3077,9 @@
       <c r="B173" s="5">
         <v>38473</v>
       </c>
+      <c r="C173" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E173" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2563,6 +3092,9 @@
       <c r="B174" s="5">
         <v>38504</v>
       </c>
+      <c r="C174" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E174" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2575,6 +3107,9 @@
       <c r="B175" s="5">
         <v>38534</v>
       </c>
+      <c r="C175" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E175" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2587,6 +3122,9 @@
       <c r="B176" s="5">
         <v>38565</v>
       </c>
+      <c r="C176" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E176" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2599,6 +3137,9 @@
       <c r="B177" s="5">
         <v>38596</v>
       </c>
+      <c r="C177" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E177" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2611,6 +3152,9 @@
       <c r="B178" s="5">
         <v>38626</v>
       </c>
+      <c r="C178" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E178" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2623,6 +3167,9 @@
       <c r="B179" s="5">
         <v>38657</v>
       </c>
+      <c r="C179" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E179" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2635,6 +3182,9 @@
       <c r="B180" s="5">
         <v>38687</v>
       </c>
+      <c r="C180" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E180" s="3">
         <v>2.4E-2</v>
       </c>
@@ -2647,6 +3197,9 @@
       <c r="B181" s="5">
         <v>38718</v>
       </c>
+      <c r="C181" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E181" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2659,6 +3212,9 @@
       <c r="B182" s="5">
         <v>38749</v>
       </c>
+      <c r="C182" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E182" s="3">
         <v>2.4E-2</v>
       </c>
@@ -2671,6 +3227,9 @@
       <c r="B183" s="5">
         <v>38777</v>
       </c>
+      <c r="C183" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E183" s="3">
         <v>2.3E-2</v>
       </c>
@@ -2683,6 +3242,9 @@
       <c r="B184" s="5">
         <v>38808</v>
       </c>
+      <c r="C184" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E184" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -2695,6 +3257,9 @@
       <c r="B185" s="5">
         <v>38838</v>
       </c>
+      <c r="C185" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E185" s="3">
         <v>2.4E-2</v>
       </c>
@@ -2707,6 +3272,9 @@
       <c r="B186" s="5">
         <v>38869</v>
       </c>
+      <c r="C186" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E186" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2719,6 +3287,9 @@
       <c r="B187" s="5">
         <v>38899</v>
       </c>
+      <c r="C187" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E187" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2731,6 +3302,9 @@
       <c r="B188" s="5">
         <v>38930</v>
       </c>
+      <c r="C188" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E188" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2743,6 +3317,9 @@
       <c r="B189" s="5">
         <v>38961</v>
       </c>
+      <c r="C189" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E189" s="3">
         <v>2.3E-2</v>
       </c>
@@ -2755,6 +3332,9 @@
       <c r="B190" s="5">
         <v>38991</v>
       </c>
+      <c r="C190" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E190" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -2767,6 +3347,9 @@
       <c r="B191" s="5">
         <v>39022</v>
       </c>
+      <c r="C191" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E191" s="3">
         <v>1.6E-2</v>
       </c>
@@ -2779,6 +3362,9 @@
       <c r="B192" s="5">
         <v>39052</v>
       </c>
+      <c r="C192" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E192" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -2791,6 +3377,9 @@
       <c r="B193" s="5">
         <v>39083</v>
       </c>
+      <c r="C193" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E193" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2803,6 +3392,9 @@
       <c r="B194" s="5">
         <v>39114</v>
       </c>
+      <c r="C194" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E194" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2815,6 +3407,9 @@
       <c r="B195" s="5">
         <v>39142</v>
       </c>
+      <c r="C195" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E195" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -2827,6 +3422,9 @@
       <c r="B196" s="5">
         <v>39173</v>
       </c>
+      <c r="C196" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E196" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2839,6 +3437,9 @@
       <c r="B197" s="5">
         <v>39203</v>
       </c>
+      <c r="C197" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E197" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -2851,6 +3452,9 @@
       <c r="B198" s="5">
         <v>39234</v>
       </c>
+      <c r="C198" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E198" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2863,6 +3467,9 @@
       <c r="B199" s="5">
         <v>39264</v>
       </c>
+      <c r="C199" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E199" s="3">
         <v>1.9E-2</v>
       </c>
@@ -2875,6 +3482,9 @@
       <c r="B200" s="5">
         <v>39295</v>
       </c>
+      <c r="C200" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E200" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -2887,6 +3497,9 @@
       <c r="B201" s="5">
         <v>39326</v>
       </c>
+      <c r="C201" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E201" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -2899,6 +3512,9 @@
       <c r="B202" s="5">
         <v>39356</v>
       </c>
+      <c r="C202" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E202" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -2911,6 +3527,9 @@
       <c r="B203" s="5">
         <v>39387</v>
       </c>
+      <c r="C203" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E203" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -2923,6 +3542,9 @@
       <c r="B204" s="5">
         <v>39417</v>
       </c>
+      <c r="C204" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E204" s="3">
         <v>0.03</v>
       </c>
@@ -2935,6 +3557,9 @@
       <c r="B205" s="5">
         <v>39448</v>
       </c>
+      <c r="C205" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E205" s="3">
         <v>3.1E-2</v>
       </c>
@@ -2947,6 +3572,9 @@
       <c r="B206" s="5">
         <v>39507</v>
       </c>
+      <c r="C206" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E206" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -2962,6 +3590,9 @@
       <c r="B207" s="5">
         <v>39510</v>
       </c>
+      <c r="C207" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E207" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -2977,6 +3608,9 @@
       <c r="B208" s="5">
         <v>39521</v>
       </c>
+      <c r="C208" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E208" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -2992,6 +3626,9 @@
       <c r="B209" s="5">
         <v>39538</v>
       </c>
+      <c r="C209" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E209" s="3">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -3007,6 +3644,9 @@
       <c r="B210" s="5">
         <v>39554</v>
       </c>
+      <c r="C210" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E210" s="3">
         <v>3.5999999999999997E-2</v>
       </c>
@@ -3022,6 +3662,9 @@
       <c r="B211" s="5">
         <v>39568</v>
       </c>
+      <c r="C211" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E211" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -3037,6 +3680,9 @@
       <c r="B212" s="5">
         <v>39583</v>
       </c>
+      <c r="C212" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E212" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
@@ -3052,6 +3698,9 @@
       <c r="B213" s="5">
         <v>39615</v>
       </c>
+      <c r="C213" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E213" s="3">
         <v>3.6999999999999998E-2</v>
       </c>
@@ -3067,6 +3716,9 @@
       <c r="B214" s="5">
         <v>39629</v>
       </c>
+      <c r="C214" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E214" s="3">
         <v>0.04</v>
       </c>
@@ -3079,6 +3731,9 @@
       <c r="B215" s="5">
         <v>39645</v>
       </c>
+      <c r="C215" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E215" s="3">
         <v>0.04</v>
       </c>
@@ -3094,6 +3749,9 @@
       <c r="B216" s="5">
         <v>39660</v>
       </c>
+      <c r="C216" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E216" s="3">
         <v>4.1000000000000002E-2</v>
       </c>
@@ -3109,6 +3767,9 @@
       <c r="B217" s="5">
         <v>39674</v>
       </c>
+      <c r="C217" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E217" s="3">
         <v>0.04</v>
       </c>
@@ -3124,6 +3785,9 @@
       <c r="B218" s="5">
         <v>39689</v>
       </c>
+      <c r="C218" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E218" s="3">
         <v>3.7999999999999999E-2</v>
       </c>
@@ -3139,6 +3803,9 @@
       <c r="B219" s="5">
         <v>39707</v>
       </c>
+      <c r="C219" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E219" s="3">
         <v>3.7999999999999999E-2</v>
       </c>
@@ -3154,6 +3821,9 @@
       <c r="B220" s="5">
         <v>39721</v>
       </c>
+      <c r="C220" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E220" s="3">
         <v>3.5999999999999997E-2</v>
       </c>
@@ -3169,6 +3839,9 @@
       <c r="B221" s="5">
         <v>39736</v>
       </c>
+      <c r="C221" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E221" s="3">
         <v>3.5999999999999997E-2</v>
       </c>
@@ -3184,6 +3857,9 @@
       <c r="B222" s="5">
         <v>39752</v>
       </c>
+      <c r="C222" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E222" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -3199,6 +3875,9 @@
       <c r="B223" s="5">
         <v>39766</v>
       </c>
+      <c r="C223" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E223" s="3">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -3214,6 +3893,9 @@
       <c r="B224" s="5">
         <v>39780</v>
       </c>
+      <c r="C224" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E224" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -3229,6 +3911,9 @@
       <c r="B225" s="5">
         <v>39799</v>
       </c>
+      <c r="C225" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E225" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -3244,6 +3929,9 @@
       <c r="B226" s="5">
         <v>39819</v>
       </c>
+      <c r="C226" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E226" s="3">
         <v>1.6E-2</v>
       </c>
@@ -3259,6 +3947,9 @@
       <c r="B227" s="5">
         <v>39828</v>
       </c>
+      <c r="C227" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E227" s="3">
         <v>1.6E-2</v>
       </c>
@@ -3274,6 +3965,9 @@
       <c r="B228" s="5">
         <v>39843</v>
       </c>
+      <c r="C228" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E228" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -3289,6 +3983,9 @@
       <c r="B229" s="5">
         <v>39871</v>
       </c>
+      <c r="C229" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E229" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -3304,6 +4001,9 @@
       <c r="B230" s="5">
         <v>39874</v>
       </c>
+      <c r="C230" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E230" s="3">
         <v>1.2E-2</v>
       </c>
@@ -3319,6 +4019,9 @@
       <c r="B231" s="5">
         <v>39888</v>
       </c>
+      <c r="C231" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E231" s="3">
         <v>1.2E-2</v>
       </c>
@@ -3334,6 +4037,9 @@
       <c r="B232" s="5">
         <v>39903</v>
       </c>
+      <c r="C232" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E232" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -3346,6 +4052,9 @@
       <c r="B233" s="5">
         <v>39919</v>
       </c>
+      <c r="C233" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E233" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -3361,6 +4070,9 @@
       <c r="B234" s="5">
         <v>39933</v>
       </c>
+      <c r="C234" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E234" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -3376,6 +4088,9 @@
       <c r="B235" s="5">
         <v>39948</v>
       </c>
+      <c r="C235" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E235" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -3391,6 +4106,9 @@
       <c r="B236" s="5">
         <v>39962</v>
       </c>
+      <c r="C236" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E236" s="3">
         <v>0</v>
       </c>
@@ -3406,6 +4124,9 @@
       <c r="B237" s="5">
         <v>39980</v>
       </c>
+      <c r="C237" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E237" s="3">
         <v>0</v>
       </c>
@@ -3421,6 +4142,9 @@
       <c r="B238" s="5">
         <v>39994</v>
       </c>
+      <c r="C238" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E238" s="3">
         <v>-1E-3</v>
       </c>
@@ -3436,6 +4160,9 @@
       <c r="B239" s="5">
         <v>40009</v>
       </c>
+      <c r="C239" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E239" s="3">
         <v>-1E-3</v>
       </c>
@@ -3451,6 +4178,9 @@
       <c r="B240" s="5">
         <v>40025</v>
       </c>
+      <c r="C240" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E240" s="3">
         <v>-6.0000000000000001E-3</v>
       </c>
@@ -3466,6 +4196,9 @@
       <c r="B241" s="5">
         <v>40039</v>
       </c>
+      <c r="C241" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E241" s="3">
         <v>-7.0000000000000001E-3</v>
       </c>
@@ -3481,6 +4214,9 @@
       <c r="B242" s="5">
         <v>40056</v>
       </c>
+      <c r="C242" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E242" s="3">
         <v>-2E-3</v>
       </c>
@@ -3496,6 +4232,9 @@
       <c r="B243" s="5">
         <v>40072</v>
       </c>
+      <c r="C243" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E243" s="3">
         <v>-2E-3</v>
       </c>
@@ -3511,6 +4250,9 @@
       <c r="B244" s="5">
         <v>40086</v>
       </c>
+      <c r="C244" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E244" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -3526,6 +4268,9 @@
       <c r="B245" s="5">
         <v>40101</v>
       </c>
+      <c r="C245" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E245" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -3541,6 +4286,9 @@
       <c r="B246" s="5">
         <v>40116</v>
       </c>
+      <c r="C246" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E246" s="3">
         <v>-1E-3</v>
       </c>
@@ -3556,6 +4304,9 @@
       <c r="B247" s="5">
         <v>40133</v>
       </c>
+      <c r="C247" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E247" s="3">
         <v>-1E-3</v>
       </c>
@@ -3571,6 +4322,9 @@
       <c r="B248" s="5">
         <v>40147</v>
       </c>
+      <c r="C248" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E248" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -3586,6 +4340,9 @@
       <c r="B249" s="5">
         <v>40163</v>
       </c>
+      <c r="C249" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E249" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -3601,6 +4358,9 @@
       <c r="B250" s="5">
         <v>40183</v>
       </c>
+      <c r="C250" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E250" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -3616,6 +4376,9 @@
       <c r="B251" s="5">
         <v>40193</v>
       </c>
+      <c r="C251" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E251" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -3631,6 +4394,9 @@
       <c r="B252" s="5">
         <v>40207</v>
       </c>
+      <c r="C252" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E252" s="3">
         <v>0.01</v>
       </c>
@@ -3646,6 +4412,9 @@
       <c r="B253" s="5">
         <v>40235</v>
       </c>
+      <c r="C253" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E253" s="3">
         <v>0.01</v>
       </c>
@@ -3661,6 +4430,9 @@
       <c r="B254" s="5">
         <v>40239</v>
       </c>
+      <c r="C254" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E254" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -3676,6 +4448,9 @@
       <c r="B255" s="5">
         <v>40253</v>
       </c>
+      <c r="C255" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E255" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -3691,6 +4466,9 @@
       <c r="B256" s="5">
         <v>40268</v>
       </c>
+      <c r="C256" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E256" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -3706,6 +4484,9 @@
       <c r="B257" s="5">
         <v>40284</v>
       </c>
+      <c r="C257" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E257" s="3">
         <v>1.4E-2</v>
       </c>
@@ -3721,6 +4502,9 @@
       <c r="B258" s="5">
         <v>40298</v>
       </c>
+      <c r="C258" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E258" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -3736,6 +4520,9 @@
       <c r="B259" s="5">
         <v>40316</v>
       </c>
+      <c r="C259" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E259" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -3751,6 +4538,9 @@
       <c r="B260" s="5">
         <v>40329</v>
       </c>
+      <c r="C260" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E260" s="3">
         <v>1.6E-2</v>
       </c>
@@ -3766,6 +4556,9 @@
       <c r="B261" s="5">
         <v>40345</v>
       </c>
+      <c r="C261" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E261" s="3">
         <v>1.6E-2</v>
       </c>
@@ -3781,6 +4574,9 @@
       <c r="B262" s="5">
         <v>40359</v>
       </c>
+      <c r="C262" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E262" s="3">
         <v>1.4E-2</v>
       </c>
@@ -3796,6 +4592,9 @@
       <c r="B263" s="5">
         <v>40373</v>
       </c>
+      <c r="C263" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E263" s="3">
         <v>1.4E-2</v>
       </c>
@@ -3811,6 +4610,9 @@
       <c r="B264" s="5">
         <v>40389</v>
       </c>
+      <c r="C264" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E264" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -3826,6 +4628,9 @@
       <c r="B265" s="5">
         <v>40406</v>
       </c>
+      <c r="C265" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E265" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -3841,6 +4646,9 @@
       <c r="B266" s="5">
         <v>40421</v>
       </c>
+      <c r="C266" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E266" s="3">
         <v>1.6E-2</v>
       </c>
@@ -3856,6 +4664,9 @@
       <c r="B267" s="5">
         <v>40436</v>
       </c>
+      <c r="C267" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E267" s="3">
         <v>1.6E-2</v>
       </c>
@@ -3871,6 +4682,9 @@
       <c r="B268" s="5">
         <v>40451</v>
       </c>
+      <c r="C268" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E268" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -3886,6 +4700,9 @@
       <c r="B269" s="5">
         <v>40466</v>
       </c>
+      <c r="C269" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E269" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -3901,6 +4718,9 @@
       <c r="B270" s="5">
         <v>40480</v>
       </c>
+      <c r="C270" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E270" s="3">
         <v>1.9E-2</v>
       </c>
@@ -3916,6 +4736,9 @@
       <c r="B271" s="5">
         <v>40498</v>
       </c>
+      <c r="C271" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E271" s="3">
         <v>1.9E-2</v>
       </c>
@@ -3931,6 +4754,9 @@
       <c r="B272" s="5">
         <v>40512</v>
       </c>
+      <c r="C272" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E272" s="3">
         <v>1.9E-2</v>
       </c>
@@ -3946,6 +4772,9 @@
       <c r="B273" s="5">
         <v>40528</v>
       </c>
+      <c r="C273" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E273" s="3">
         <v>1.9E-2</v>
       </c>
@@ -3961,6 +4790,9 @@
       <c r="B274" s="5">
         <v>40547</v>
       </c>
+      <c r="C274" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E274" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -3976,6 +4808,9 @@
       <c r="B275" s="5">
         <v>40557</v>
       </c>
+      <c r="C275" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E275" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -3991,6 +4826,9 @@
       <c r="B276" s="5">
         <v>40574</v>
       </c>
+      <c r="C276" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E276" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4006,6 +4844,9 @@
       <c r="B277" s="5">
         <v>40602</v>
       </c>
+      <c r="C277" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E277" s="3">
         <v>2.3E-2</v>
       </c>
@@ -4021,6 +4862,9 @@
       <c r="B278" s="5">
         <v>40603</v>
       </c>
+      <c r="C278" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E278" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4036,6 +4880,9 @@
       <c r="B279" s="5">
         <v>40618</v>
       </c>
+      <c r="C279" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E279" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4051,6 +4898,9 @@
       <c r="B280" s="5">
         <v>40633</v>
       </c>
+      <c r="C280" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E280" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -4066,6 +4916,9 @@
       <c r="B281" s="5">
         <v>40648</v>
       </c>
+      <c r="C281" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E281" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4081,6 +4934,9 @@
       <c r="B282" s="5">
         <v>40662</v>
       </c>
+      <c r="C282" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E282" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -4096,6 +4952,9 @@
       <c r="B283" s="5">
         <v>40679</v>
       </c>
+      <c r="C283" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E283" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -4111,6 +4970,9 @@
       <c r="B284" s="5">
         <v>40694</v>
       </c>
+      <c r="C284" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E284" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4126,6 +4988,9 @@
       <c r="B285" s="5">
         <v>40710</v>
       </c>
+      <c r="C285" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E285" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4141,6 +5006,9 @@
       <c r="B286" s="5">
         <v>40724</v>
       </c>
+      <c r="C286" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E286" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4156,6 +5024,9 @@
       <c r="B287" s="5">
         <v>40738</v>
       </c>
+      <c r="C287" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E287" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4171,6 +5042,9 @@
       <c r="B288" s="5">
         <v>40753</v>
       </c>
+      <c r="C288" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E288" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -4186,6 +5060,9 @@
       <c r="B289" s="5">
         <v>40772</v>
       </c>
+      <c r="C289" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E289" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -4201,6 +5078,9 @@
       <c r="B290" s="5">
         <v>40786</v>
       </c>
+      <c r="C290" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E290" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -4216,6 +5096,9 @@
       <c r="B291" s="5">
         <v>40801</v>
       </c>
+      <c r="C291" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E291" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -4231,6 +5114,9 @@
       <c r="B292" s="5">
         <v>40816</v>
       </c>
+      <c r="C292" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E292" s="3">
         <v>0.03</v>
       </c>
@@ -4246,6 +5132,9 @@
       <c r="B293" s="5">
         <v>40830</v>
       </c>
+      <c r="C293" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E293" s="3">
         <v>0.03</v>
       </c>
@@ -4261,6 +5150,9 @@
       <c r="B294" s="5">
         <v>40847</v>
       </c>
+      <c r="C294" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E294" s="3">
         <v>0.03</v>
       </c>
@@ -4276,6 +5168,9 @@
       <c r="B295" s="5">
         <v>40863</v>
       </c>
+      <c r="C295" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E295" s="3">
         <v>0.03</v>
       </c>
@@ -4291,6 +5186,9 @@
       <c r="B296" s="5">
         <v>40877</v>
       </c>
+      <c r="C296" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E296" s="3">
         <v>0.03</v>
       </c>
@@ -4306,6 +5204,9 @@
       <c r="B297" s="5">
         <v>40892</v>
       </c>
+      <c r="C297" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E297" s="3">
         <v>0.03</v>
       </c>
@@ -4321,6 +5222,9 @@
       <c r="B298" s="5">
         <v>40912</v>
       </c>
+      <c r="C298" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E298" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -4336,6 +5240,9 @@
       <c r="B299" s="5">
         <v>40925</v>
       </c>
+      <c r="C299" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E299" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4351,6 +5258,9 @@
       <c r="B300" s="5">
         <v>40940</v>
       </c>
+      <c r="C300" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E300" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4366,6 +5276,9 @@
       <c r="B301" s="5">
         <v>40968</v>
       </c>
+      <c r="C301" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E301" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -4381,6 +5294,9 @@
       <c r="B302" s="5">
         <v>40969</v>
       </c>
+      <c r="C302" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E302" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4396,6 +5312,9 @@
       <c r="B303" s="5">
         <v>40982</v>
       </c>
+      <c r="C303" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E303" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4411,6 +5330,9 @@
       <c r="B304" s="5">
         <v>40998</v>
       </c>
+      <c r="C304" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E304" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -4426,6 +5348,9 @@
       <c r="B305" s="5">
         <v>41016</v>
       </c>
+      <c r="C305" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E305" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4441,6 +5366,9 @@
       <c r="B306" s="5">
         <v>41029</v>
       </c>
+      <c r="C306" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E306" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -4456,6 +5384,9 @@
       <c r="B307" s="5">
         <v>41045</v>
       </c>
+      <c r="C307" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E307" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -4471,6 +5402,9 @@
       <c r="B308" s="5">
         <v>41060</v>
       </c>
+      <c r="C308" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E308" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4486,6 +5420,9 @@
       <c r="B309" s="5">
         <v>41074</v>
       </c>
+      <c r="C309" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E309" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4501,6 +5438,9 @@
       <c r="B310" s="5">
         <v>41089</v>
       </c>
+      <c r="C310" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E310" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4516,6 +5456,9 @@
       <c r="B311" s="5">
         <v>41106</v>
       </c>
+      <c r="C311" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E311" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4531,6 +5474,9 @@
       <c r="B312" s="5">
         <v>41121</v>
       </c>
+      <c r="C312" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E312" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4546,6 +5492,9 @@
       <c r="B313" s="5">
         <v>41137</v>
       </c>
+      <c r="C313" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E313" s="3">
         <v>2.4E-2</v>
       </c>
@@ -4561,6 +5510,9 @@
       <c r="B314" s="5">
         <v>41152</v>
       </c>
+      <c r="C314" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E314" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -4576,6 +5528,9 @@
       <c r="B315" s="5">
         <v>41166</v>
       </c>
+      <c r="C315" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E315" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -4591,6 +5546,9 @@
       <c r="B316" s="5">
         <v>41180</v>
       </c>
+      <c r="C316" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E316" s="3">
         <v>2.7E-2</v>
       </c>
@@ -4606,6 +5564,9 @@
       <c r="B317" s="5">
         <v>41198</v>
       </c>
+      <c r="C317" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E317" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -4621,6 +5582,9 @@
       <c r="B318" s="5">
         <v>41213</v>
       </c>
+      <c r="C318" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E318" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -4636,6 +5600,9 @@
       <c r="B319" s="5">
         <v>41228</v>
       </c>
+      <c r="C319" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E319" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -4651,6 +5618,9 @@
       <c r="B320" s="5">
         <v>41243</v>
       </c>
+      <c r="C320" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E320" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -4666,6 +5636,9 @@
       <c r="B321" s="5">
         <v>41257</v>
       </c>
+      <c r="C321" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E321" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -4681,6 +5654,9 @@
       <c r="B322" s="5">
         <v>41278</v>
       </c>
+      <c r="C322" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E322" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -4696,6 +5672,9 @@
       <c r="B323" s="5">
         <v>41290</v>
       </c>
+      <c r="C323" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E323" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -4711,6 +5690,9 @@
       <c r="B324" s="5">
         <v>41306</v>
       </c>
+      <c r="C324" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E324" s="3">
         <v>0.02</v>
       </c>
@@ -4726,6 +5708,9 @@
       <c r="B325" s="5">
         <v>41333</v>
       </c>
+      <c r="C325" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E325" s="3">
         <v>0.02</v>
       </c>
@@ -4741,6 +5726,9 @@
       <c r="B326" s="5">
         <v>41348</v>
       </c>
+      <c r="C326" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E326" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -4756,6 +5744,9 @@
       <c r="B327" s="5">
         <v>41367</v>
       </c>
+      <c r="C327" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E327" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -4771,6 +5762,9 @@
       <c r="B328" s="5">
         <v>41380</v>
       </c>
+      <c r="C328" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E328" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -4786,6 +5780,9 @@
       <c r="B329" s="5">
         <v>41394</v>
       </c>
+      <c r="C329" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E329" s="3">
         <v>1.2E-2</v>
       </c>
@@ -4801,6 +5798,9 @@
       <c r="B330" s="5">
         <v>41410</v>
       </c>
+      <c r="C330" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E330" s="3">
         <v>1.2E-2</v>
       </c>
@@ -4816,6 +5816,9 @@
       <c r="B331" s="5">
         <v>41425</v>
       </c>
+      <c r="C331" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E331" s="3">
         <v>1.4E-2</v>
       </c>
@@ -4831,6 +5834,9 @@
       <c r="B332" s="5">
         <v>41439</v>
       </c>
+      <c r="C332" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E332" s="3">
         <v>1.4E-2</v>
       </c>
@@ -4846,6 +5852,9 @@
       <c r="B333" s="5">
         <v>41456</v>
       </c>
+      <c r="C333" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E333" s="3">
         <v>1.6E-2</v>
       </c>
@@ -4861,6 +5870,9 @@
       <c r="B334" s="5">
         <v>41471</v>
       </c>
+      <c r="C334" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E334" s="3">
         <v>1.6E-2</v>
       </c>
@@ -4876,6 +5888,9 @@
       <c r="B335" s="5">
         <v>41486</v>
       </c>
+      <c r="C335" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E335" s="3">
         <v>1.6E-2</v>
       </c>
@@ -4891,6 +5906,9 @@
       <c r="B336" s="5">
         <v>41502</v>
       </c>
+      <c r="C336" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E336" s="3">
         <v>1.6E-2</v>
       </c>
@@ -4906,6 +5924,9 @@
       <c r="B337" s="5">
         <v>41516</v>
       </c>
+      <c r="C337" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E337" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -4921,6 +5942,9 @@
       <c r="B338" s="5">
         <v>41533</v>
       </c>
+      <c r="C338" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E338" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -4936,6 +5960,9 @@
       <c r="B339" s="5">
         <v>41547</v>
       </c>
+      <c r="C339" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E339" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -4951,6 +5978,9 @@
       <c r="B340" s="5">
         <v>41563</v>
       </c>
+      <c r="C340" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E340" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -4966,6 +5996,9 @@
       <c r="B341" s="5">
         <v>41578</v>
       </c>
+      <c r="C341" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E341" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -4981,6 +6014,9 @@
       <c r="B342" s="5">
         <v>41593</v>
       </c>
+      <c r="C342" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E342" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -4996,6 +6032,9 @@
       <c r="B343" s="5">
         <v>41607</v>
       </c>
+      <c r="C343" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E343" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -5011,6 +6050,9 @@
       <c r="B344" s="5">
         <v>41625</v>
       </c>
+      <c r="C344" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E344" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -5026,6 +6068,9 @@
       <c r="B345" s="5">
         <v>41646</v>
       </c>
+      <c r="C345" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E345" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -5041,6 +6086,9 @@
       <c r="B346" s="5">
         <v>41655</v>
       </c>
+      <c r="C346" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E346" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -5056,6 +6104,9 @@
       <c r="B347" s="5">
         <v>41670</v>
       </c>
+      <c r="C347" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E347" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -5071,6 +6122,9 @@
       <c r="B348" s="5">
         <v>41694</v>
       </c>
+      <c r="C348" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E348" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -5086,6 +6140,9 @@
       <c r="B349" s="5">
         <v>41698</v>
       </c>
+      <c r="C349" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E349" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -5101,6 +6158,9 @@
       <c r="B350" s="5">
         <v>41715</v>
       </c>
+      <c r="C350" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E350" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -5116,6 +6176,9 @@
       <c r="B351" s="5">
         <v>41729</v>
       </c>
+      <c r="C351" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E351" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -5131,6 +6194,9 @@
       <c r="B352" s="5">
         <v>41745</v>
       </c>
+      <c r="C352" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E352" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -5146,6 +6212,9 @@
       <c r="B353" s="5">
         <v>41759</v>
       </c>
+      <c r="C353" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E353" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -5161,6 +6230,9 @@
       <c r="B354" s="5">
         <v>41774</v>
       </c>
+      <c r="C354" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E354" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -5176,6 +6248,9 @@
       <c r="B355" s="5">
         <v>41793</v>
       </c>
+      <c r="C355" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E355" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -5191,6 +6266,9 @@
       <c r="B356" s="5">
         <v>41806</v>
       </c>
+      <c r="C356" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E356" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -5206,6 +6284,9 @@
       <c r="B357" s="5">
         <v>41820</v>
       </c>
+      <c r="C357" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E357" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -5221,6 +6302,9 @@
       <c r="B358" s="5">
         <v>41837</v>
       </c>
+      <c r="C358" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E358" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -5236,6 +6320,9 @@
       <c r="B359" s="5">
         <v>41851</v>
       </c>
+      <c r="C359" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E359" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -5251,6 +6338,9 @@
       <c r="B360" s="5">
         <v>41865</v>
       </c>
+      <c r="C360" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E360" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -5266,6 +6356,9 @@
       <c r="B361" s="5">
         <v>41880</v>
       </c>
+      <c r="C361" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E361" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -5281,6 +6374,9 @@
       <c r="B362" s="5">
         <v>41899</v>
       </c>
+      <c r="C362" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E362" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -5296,6 +6392,9 @@
       <c r="B363" s="5">
         <v>41912</v>
       </c>
+      <c r="C363" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E363" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -5311,6 +6410,9 @@
       <c r="B364" s="5">
         <v>41928</v>
       </c>
+      <c r="C364" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E364" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -5326,6 +6428,9 @@
       <c r="B365" s="5">
         <v>41943</v>
       </c>
+      <c r="C365" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E365" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -5341,6 +6446,9 @@
       <c r="B366" s="5">
         <v>41957</v>
       </c>
+      <c r="C366" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E366" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -5356,6 +6464,9 @@
       <c r="B367" s="5">
         <v>41971</v>
       </c>
+      <c r="C367" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E367" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -5371,6 +6482,9 @@
       <c r="B368" s="5">
         <v>41990</v>
       </c>
+      <c r="C368" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E368" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -5386,6 +6500,9 @@
       <c r="B369" s="5">
         <v>42011</v>
       </c>
+      <c r="C369" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E369" s="3">
         <v>-2E-3</v>
       </c>
@@ -5401,6 +6518,9 @@
       <c r="B370" s="5">
         <v>42020</v>
       </c>
+      <c r="C370" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E370" s="3">
         <v>-2E-3</v>
       </c>
@@ -5416,6 +6536,9 @@
       <c r="B371" s="5">
         <v>42034</v>
       </c>
+      <c r="C371" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E371" s="3">
         <v>-6.0000000000000001E-3</v>
       </c>
@@ -5431,6 +6554,9 @@
       <c r="B372" s="5">
         <v>42059</v>
       </c>
+      <c r="C372" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E372" s="3">
         <v>-6.0000000000000001E-3</v>
       </c>
@@ -5446,6 +6572,9 @@
       <c r="B373" s="5">
         <v>42065</v>
       </c>
+      <c r="C373" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E373" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -5461,6 +6590,9 @@
       <c r="B374" s="5">
         <v>42080</v>
       </c>
+      <c r="C374" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E374" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -5476,6 +6608,9 @@
       <c r="B375" s="5">
         <v>42094</v>
       </c>
+      <c r="C375" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E375" s="3">
         <v>-1E-3</v>
       </c>
@@ -5491,6 +6626,9 @@
       <c r="B376" s="5">
         <v>42111</v>
       </c>
+      <c r="C376" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E376" s="3">
         <v>-1E-3</v>
       </c>
@@ -5506,6 +6644,9 @@
       <c r="B377" s="5">
         <v>42124</v>
       </c>
+      <c r="C377" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E377" s="3">
         <v>0</v>
       </c>
@@ -5521,6 +6662,9 @@
       <c r="B378" s="5">
         <v>42143</v>
       </c>
+      <c r="C378" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E378" s="3">
         <v>0</v>
       </c>
@@ -5536,6 +6680,9 @@
       <c r="B379" s="5">
         <v>42157</v>
       </c>
+      <c r="C379" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E379" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -5551,6 +6698,9 @@
       <c r="B380" s="5">
         <v>42172</v>
       </c>
+      <c r="C380" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E380" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -5566,6 +6716,9 @@
       <c r="B381" s="5">
         <v>42185</v>
       </c>
+      <c r="C381" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E381" s="3">
         <v>2E-3</v>
       </c>
@@ -5581,6 +6734,9 @@
       <c r="B382" s="5">
         <v>42201</v>
       </c>
+      <c r="C382" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E382" s="3">
         <v>2E-3</v>
       </c>
@@ -5596,6 +6752,9 @@
       <c r="B383" s="5">
         <v>42216</v>
       </c>
+      <c r="C383" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E383" s="3">
         <v>2E-3</v>
       </c>
@@ -5611,6 +6770,9 @@
       <c r="B384" s="5">
         <v>42230</v>
       </c>
+      <c r="C384" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E384" s="3">
         <v>2E-3</v>
       </c>
@@ -5626,6 +6788,9 @@
       <c r="B385" s="5">
         <v>42247</v>
       </c>
+      <c r="C385" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E385" s="3">
         <v>2E-3</v>
       </c>
@@ -5641,6 +6806,9 @@
       <c r="B386" s="5">
         <v>42263</v>
       </c>
+      <c r="C386" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E386" s="3">
         <v>1E-3</v>
       </c>
@@ -5656,6 +6824,9 @@
       <c r="B387" s="5">
         <v>42277</v>
       </c>
+      <c r="C387" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E387" s="3">
         <v>-1E-3</v>
       </c>
@@ -5671,6 +6842,9 @@
       <c r="B388" s="5">
         <v>42293</v>
       </c>
+      <c r="C388" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E388" s="3">
         <v>-1E-3</v>
       </c>
@@ -5686,6 +6860,9 @@
       <c r="B389" s="5">
         <v>42307</v>
       </c>
+      <c r="C389" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E389" s="3">
         <v>0</v>
       </c>
@@ -5701,6 +6878,9 @@
       <c r="B390" s="5">
         <v>42324</v>
       </c>
+      <c r="C390" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E390" s="3">
         <v>1E-3</v>
       </c>
@@ -5716,6 +6896,9 @@
       <c r="B391" s="5">
         <v>42340</v>
       </c>
+      <c r="C391" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E391" s="3">
         <v>1E-3</v>
       </c>
@@ -5731,6 +6914,9 @@
       <c r="B392" s="5">
         <v>42354</v>
       </c>
+      <c r="C392" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E392" s="3">
         <v>2E-3</v>
       </c>
@@ -5746,6 +6932,9 @@
       <c r="B393" s="5">
         <v>42374</v>
       </c>
+      <c r="C393" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E393" s="3">
         <v>2E-3</v>
       </c>
@@ -5761,6 +6950,9 @@
       <c r="B394" s="5">
         <v>42388</v>
       </c>
+      <c r="C394" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E394" s="3">
         <v>2E-3</v>
       </c>
@@ -5776,6 +6968,9 @@
       <c r="B395" s="5">
         <v>42398</v>
       </c>
+      <c r="C395" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E395" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -5791,6 +6986,9 @@
       <c r="B396" s="5">
         <v>42425</v>
       </c>
+      <c r="C396" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E396" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -5806,6 +7004,9 @@
       <c r="B397" s="5">
         <v>42429</v>
       </c>
+      <c r="C397" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E397" s="3">
         <v>-2E-3</v>
       </c>
@@ -5821,6 +7022,9 @@
       <c r="B398" s="5">
         <v>42446</v>
       </c>
+      <c r="C398" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E398" s="3">
         <v>-2E-3</v>
       </c>
@@ -5836,6 +7040,9 @@
       <c r="B399" s="5">
         <v>42460</v>
       </c>
+      <c r="C399" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E399" s="3">
         <v>-1E-3</v>
       </c>
@@ -5851,6 +7058,9 @@
       <c r="B400" s="5">
         <v>42474</v>
       </c>
+      <c r="C400" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E400" s="3">
         <v>0</v>
       </c>
@@ -5866,6 +7076,9 @@
       <c r="B401" s="5">
         <v>42489</v>
       </c>
+      <c r="C401" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E401" s="3">
         <v>-2E-3</v>
       </c>
@@ -5881,6 +7094,9 @@
       <c r="B402" s="5">
         <v>42508</v>
       </c>
+      <c r="C402" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E402" s="3">
         <v>-2E-3</v>
       </c>
@@ -5896,6 +7112,9 @@
       <c r="B403" s="5">
         <v>42521</v>
       </c>
+      <c r="C403" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E403" s="3">
         <v>-1E-3</v>
       </c>
@@ -5911,6 +7130,9 @@
       <c r="B404" s="5">
         <v>42537</v>
       </c>
+      <c r="C404" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E404" s="3">
         <v>-1E-3</v>
       </c>
@@ -5926,6 +7148,9 @@
       <c r="B405" s="5">
         <v>42551</v>
       </c>
+      <c r="C405" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E405" s="3">
         <v>1E-3</v>
       </c>
@@ -5941,6 +7166,9 @@
       <c r="B406" s="5">
         <v>42566</v>
       </c>
+      <c r="C406" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E406" s="3">
         <v>1E-3</v>
       </c>
@@ -5956,6 +7184,9 @@
       <c r="B407" s="5">
         <v>42580</v>
       </c>
+      <c r="C407" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E407" s="3">
         <v>2E-3</v>
       </c>
@@ -5971,6 +7202,9 @@
       <c r="B408" s="5">
         <v>42600</v>
       </c>
+      <c r="C408" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E408" s="3">
         <v>2E-3</v>
       </c>
@@ -5986,6 +7220,9 @@
       <c r="B409" s="5">
         <v>42613</v>
       </c>
+      <c r="C409" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E409" s="3">
         <v>2E-3</v>
       </c>
@@ -6001,6 +7238,9 @@
       <c r="B410" s="5">
         <v>42628</v>
       </c>
+      <c r="C410" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E410" s="3">
         <v>2E-3</v>
       </c>
@@ -6016,6 +7256,9 @@
       <c r="B411" s="5">
         <v>42643</v>
       </c>
+      <c r="C411" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E411" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -6031,6 +7274,9 @@
       <c r="B412" s="5">
         <v>42660</v>
       </c>
+      <c r="C412" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E412" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -6046,6 +7292,9 @@
       <c r="B413" s="5">
         <v>42674</v>
       </c>
+      <c r="C413" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E413" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -6061,6 +7310,9 @@
       <c r="B414" s="5">
         <v>42691</v>
       </c>
+      <c r="C414" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E414" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -6076,6 +7328,9 @@
       <c r="B415" s="5">
         <v>42704</v>
       </c>
+      <c r="C415" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E415" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -6091,6 +7346,9 @@
       <c r="B416" s="5">
         <v>42720</v>
       </c>
+      <c r="C416" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E416" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -6106,6 +7364,9 @@
       <c r="B417" s="5">
         <v>42739</v>
       </c>
+      <c r="C417" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E417" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -6121,6 +7382,9 @@
       <c r="B418" s="5">
         <v>42753</v>
       </c>
+      <c r="C418" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E418" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -6136,6 +7400,9 @@
       <c r="B419" s="5">
         <v>42766</v>
       </c>
+      <c r="C419" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E419" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -6151,6 +7418,9 @@
       <c r="B420" s="5">
         <v>42788</v>
       </c>
+      <c r="C420" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E420" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -6166,6 +7436,9 @@
       <c r="B421" s="5">
         <v>42796</v>
       </c>
+      <c r="C421" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E421" s="3">
         <v>0.02</v>
       </c>
@@ -6181,6 +7454,9 @@
       <c r="B422" s="5">
         <v>42810</v>
       </c>
+      <c r="C422" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E422" s="3">
         <v>0.02</v>
       </c>
@@ -6196,6 +7472,9 @@
       <c r="B423" s="5">
         <v>42825</v>
       </c>
+      <c r="C423" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E423" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6211,6 +7490,9 @@
       <c r="B424" s="5">
         <v>42844</v>
       </c>
+      <c r="C424" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E424" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6226,6 +7508,9 @@
       <c r="B425" s="5">
         <v>42853</v>
       </c>
+      <c r="C425" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E425" s="3">
         <v>1.9E-2</v>
       </c>
@@ -6241,6 +7526,9 @@
       <c r="B426" s="5">
         <v>42872</v>
       </c>
+      <c r="C426" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E426" s="3">
         <v>1.9E-2</v>
       </c>
@@ -6256,6 +7544,9 @@
       <c r="B427" s="5">
         <v>42886</v>
       </c>
+      <c r="C427" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E427" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6271,6 +7562,9 @@
       <c r="B428" s="5">
         <v>42902</v>
       </c>
+      <c r="C428" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E428" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6286,6 +7580,9 @@
       <c r="B429" s="5">
         <v>42916</v>
       </c>
+      <c r="C429" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E429" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -6301,6 +7598,9 @@
       <c r="B430" s="5">
         <v>42933</v>
       </c>
+      <c r="C430" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E430" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -6316,6 +7616,9 @@
       <c r="B431" s="5">
         <v>42947</v>
       </c>
+      <c r="C431" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E431" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -6331,6 +7634,9 @@
       <c r="B432" s="5">
         <v>42964</v>
       </c>
+      <c r="C432" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E432" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -6346,6 +7652,9 @@
       <c r="B433" s="5">
         <v>42978</v>
       </c>
+      <c r="C433" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E433" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6361,6 +7670,9 @@
       <c r="B434" s="5">
         <v>42996</v>
       </c>
+      <c r="C434" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E434" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6376,6 +7688,9 @@
       <c r="B435" s="5">
         <v>43007</v>
       </c>
+      <c r="C435" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E435" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6391,6 +7706,9 @@
       <c r="B436" s="5">
         <v>43025</v>
       </c>
+      <c r="C436" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E436" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6406,6 +7724,9 @@
       <c r="B437" s="5">
         <v>43039</v>
       </c>
+      <c r="C437" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E437" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6421,6 +7742,9 @@
       <c r="B438" s="5">
         <v>43055</v>
       </c>
+      <c r="C438" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E438" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6436,6 +7760,9 @@
       <c r="B439" s="5">
         <v>43069</v>
       </c>
+      <c r="C439" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E439" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6451,6 +7778,9 @@
       <c r="B440" s="5">
         <v>43087</v>
       </c>
+      <c r="C440" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E440" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6466,6 +7796,9 @@
       <c r="B441" s="5">
         <v>43105</v>
       </c>
+      <c r="C441" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E441" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6481,6 +7814,9 @@
       <c r="B442" s="5">
         <v>43117</v>
       </c>
+      <c r="C442" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E442" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6496,6 +7832,9 @@
       <c r="B443" s="5">
         <v>43131</v>
       </c>
+      <c r="C443" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E443" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -6511,6 +7850,9 @@
       <c r="B444" s="5">
         <v>43154</v>
       </c>
+      <c r="C444" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E444" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -6526,6 +7868,9 @@
       <c r="B445" s="5">
         <v>43159</v>
       </c>
+      <c r="C445" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E445" s="3">
         <v>1.2E-2</v>
       </c>
@@ -6541,6 +7886,9 @@
       <c r="B446" s="5">
         <v>43175</v>
       </c>
+      <c r="C446" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E446" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -6556,6 +7904,9 @@
       <c r="B447" s="5">
         <v>43194</v>
       </c>
+      <c r="C447" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E447" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6571,6 +7922,9 @@
       <c r="B448" s="5">
         <v>43208</v>
       </c>
+      <c r="C448" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E448" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -6586,6 +7940,9 @@
       <c r="B449" s="5">
         <v>43223</v>
       </c>
+      <c r="C449" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E449" s="3">
         <v>1.2E-2</v>
       </c>
@@ -6601,6 +7958,9 @@
       <c r="B450" s="5">
         <v>43236</v>
       </c>
+      <c r="C450" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E450" s="3">
         <v>1.2E-2</v>
       </c>
@@ -6616,6 +7976,9 @@
       <c r="B451" s="5">
         <v>43251</v>
       </c>
+      <c r="C451" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E451" s="3">
         <v>1.9E-2</v>
       </c>
@@ -6631,6 +7994,9 @@
       <c r="B452" s="5">
         <v>43266</v>
       </c>
+      <c r="C452" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E452" s="3">
         <v>1.9E-2</v>
       </c>
@@ -6646,6 +8012,9 @@
       <c r="B453" s="5">
         <v>43280</v>
       </c>
+      <c r="C453" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E453" s="3">
         <v>0.02</v>
       </c>
@@ -6661,6 +8030,9 @@
       <c r="B454" s="5">
         <v>43299</v>
       </c>
+      <c r="C454" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E454" s="3">
         <v>0.02</v>
       </c>
@@ -6676,6 +8048,9 @@
       <c r="B455" s="5">
         <v>43312</v>
       </c>
+      <c r="C455" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E455" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -6691,6 +8066,9 @@
       <c r="B456" s="5">
         <v>43329</v>
       </c>
+      <c r="C456" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E456" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -6706,6 +8084,9 @@
       <c r="B457" s="5">
         <v>43343</v>
       </c>
+      <c r="C457" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E457" s="3">
         <v>0.02</v>
       </c>
@@ -6721,6 +8102,9 @@
       <c r="B458" s="5">
         <v>43360</v>
       </c>
+      <c r="C458" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E458" s="3">
         <v>0.02</v>
       </c>
@@ -6736,6 +8120,9 @@
       <c r="B459" s="5">
         <v>43371</v>
       </c>
+      <c r="C459" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E459" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -6751,6 +8138,9 @@
       <c r="B460" s="5">
         <v>43390</v>
       </c>
+      <c r="C460" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E460" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -6766,6 +8156,9 @@
       <c r="B461" s="5">
         <v>43404</v>
       </c>
+      <c r="C461" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E461" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -6781,6 +8174,9 @@
       <c r="B462" s="5">
         <v>43420</v>
       </c>
+      <c r="C462" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E462" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -6796,6 +8192,9 @@
       <c r="B463" s="5">
         <v>43434</v>
       </c>
+      <c r="C463" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E463" s="3">
         <v>0.02</v>
       </c>
@@ -6811,6 +8210,9 @@
       <c r="B464" s="5">
         <v>43451</v>
       </c>
+      <c r="C464" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E464" s="3">
         <v>1.9E-2</v>
       </c>
@@ -6826,6 +8228,9 @@
       <c r="B465" s="5">
         <v>43469</v>
       </c>
+      <c r="C465" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E465" s="3">
         <v>1.6E-2</v>
       </c>
@@ -6841,6 +8246,9 @@
       <c r="B466" s="5">
         <v>43482</v>
       </c>
+      <c r="C466" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E466" s="3">
         <v>1.6E-2</v>
       </c>
@@ -6856,6 +8264,9 @@
       <c r="B467" s="5">
         <v>43497</v>
       </c>
+      <c r="C467" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E467" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6871,6 +8282,9 @@
       <c r="B468" s="5">
         <v>43518</v>
       </c>
+      <c r="C468" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E468" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6886,6 +8300,9 @@
       <c r="B469" s="5">
         <v>43525</v>
       </c>
+      <c r="C469" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E469" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6901,6 +8318,9 @@
       <c r="B470" s="5">
         <v>43539</v>
       </c>
+      <c r="C470" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E470" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6916,6 +8336,9 @@
       <c r="B471" s="5">
         <v>43553</v>
       </c>
+      <c r="C471" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="G471" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -6925,6 +8348,9 @@
       <c r="B472" s="5">
         <v>43556</v>
       </c>
+      <c r="C472" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E472" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6940,6 +8366,9 @@
       <c r="B473" s="5">
         <v>43572</v>
       </c>
+      <c r="C473" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E473" s="3">
         <v>1.4E-2</v>
       </c>
@@ -6955,6 +8384,9 @@
       <c r="B474" s="5">
         <v>43588</v>
       </c>
+      <c r="C474" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E474" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -6970,6 +8402,9 @@
       <c r="B475" s="5">
         <v>43602</v>
       </c>
+      <c r="C475" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E475" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -6985,6 +8420,9 @@
       <c r="B476" s="5">
         <v>43620</v>
       </c>
+      <c r="C476" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E476" s="3">
         <v>1.2E-2</v>
       </c>
@@ -7000,6 +8438,9 @@
       <c r="B477" s="5">
         <v>43634</v>
       </c>
+      <c r="C477" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E477" s="3">
         <v>1.2E-2</v>
       </c>
@@ -7015,6 +8456,9 @@
       <c r="B478" s="5">
         <v>43644</v>
       </c>
+      <c r="C478" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E478" s="3">
         <v>1.2E-2</v>
       </c>
@@ -7030,6 +8474,9 @@
       <c r="B479" s="5">
         <v>43663</v>
       </c>
+      <c r="C479" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E479" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -7045,6 +8492,9 @@
       <c r="B480" s="5">
         <v>43677</v>
       </c>
+      <c r="C480" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E480" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
@@ -7060,6 +8510,9 @@
       <c r="B481" s="5">
         <v>43696</v>
       </c>
+      <c r="C481" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E481" s="3">
         <v>0.01</v>
       </c>
@@ -7075,6 +8528,9 @@
       <c r="B482" s="5">
         <v>43707</v>
       </c>
+      <c r="C482" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E482" s="3">
         <v>0.01</v>
       </c>
@@ -7090,6 +8546,9 @@
       <c r="B483" s="5">
         <v>43726</v>
       </c>
+      <c r="C483" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E483" s="3">
         <v>0.01</v>
       </c>
@@ -7105,6 +8564,9 @@
       <c r="B484" s="5">
         <v>43739</v>
       </c>
+      <c r="C484" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E484" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -7120,6 +8582,9 @@
       <c r="B485" s="5">
         <v>43754</v>
       </c>
+      <c r="C485" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E485" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -7135,6 +8600,9 @@
       <c r="B486" s="5">
         <v>43769</v>
       </c>
+      <c r="C486" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E486" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -7150,6 +8618,9 @@
       <c r="B487" s="5">
         <v>43784</v>
       </c>
+      <c r="C487" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E487" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -7165,6 +8636,9 @@
       <c r="B488" s="5">
         <v>43798</v>
       </c>
+      <c r="C488" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E488" s="3">
         <v>0.01</v>
       </c>
@@ -7180,6 +8654,9 @@
       <c r="B489" s="5">
         <v>43817</v>
       </c>
+      <c r="C489" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E489" s="3">
         <v>0.01</v>
       </c>
@@ -7195,6 +8672,9 @@
       <c r="B490" s="5">
         <v>43837</v>
       </c>
+      <c r="C490" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E490" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -7210,6 +8690,9 @@
       <c r="B491" s="5">
         <v>43847</v>
       </c>
+      <c r="C491" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E491" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -7225,6 +8708,9 @@
       <c r="B492" s="5">
         <v>43861</v>
       </c>
+      <c r="C492" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E492" s="3">
         <v>1.4E-2</v>
       </c>
@@ -7240,6 +8726,9 @@
       <c r="B493" s="5">
         <v>43882</v>
       </c>
+      <c r="C493" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E493" s="3">
         <v>1.4E-2</v>
       </c>
@@ -7255,6 +8744,9 @@
       <c r="B494" s="5">
         <v>43893</v>
       </c>
+      <c r="C494" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E494" s="3">
         <v>1.2E-2</v>
       </c>
@@ -7270,6 +8762,9 @@
       <c r="B495" s="5">
         <v>43908</v>
       </c>
+      <c r="C495" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E495" s="3">
         <v>1.2E-2</v>
       </c>
@@ -7285,6 +8780,9 @@
       <c r="B496" s="5">
         <v>43921</v>
       </c>
+      <c r="C496" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E496" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -7300,6 +8798,9 @@
       <c r="B497" s="5">
         <v>43938</v>
       </c>
+      <c r="C497" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E497" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
@@ -7315,6 +8816,9 @@
       <c r="B498" s="5">
         <v>43951</v>
       </c>
+      <c r="C498" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E498" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -7330,6 +8834,9 @@
       <c r="B499" s="5">
         <v>43971</v>
       </c>
+      <c r="C499" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E499" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -7345,6 +8852,9 @@
       <c r="B500" s="5">
         <v>43980</v>
       </c>
+      <c r="C500" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E500" s="3">
         <v>1E-3</v>
       </c>
@@ -7360,6 +8870,9 @@
       <c r="B501" s="5">
         <v>43999</v>
       </c>
+      <c r="C501" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E501" s="3">
         <v>1E-3</v>
       </c>
@@ -7375,6 +8888,9 @@
       <c r="B502" s="5">
         <v>44012</v>
       </c>
+      <c r="C502" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E502" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -7390,6 +8906,9 @@
       <c r="B503" s="5">
         <v>44029</v>
       </c>
+      <c r="C503" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E503" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
@@ -7405,6 +8924,9 @@
       <c r="B504" s="5">
         <v>44043</v>
       </c>
+      <c r="C504" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E504" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -7420,6 +8942,9 @@
       <c r="B505" s="5">
         <v>44062</v>
       </c>
+      <c r="C505" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E505" s="3">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -7435,6 +8960,9 @@
       <c r="B506" s="5">
         <v>44075</v>
       </c>
+      <c r="C506" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E506" s="3">
         <v>-2E-3</v>
       </c>
@@ -7450,6 +8978,9 @@
       <c r="B507" s="5">
         <v>44091</v>
       </c>
+      <c r="C507" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E507" s="3">
         <v>-2E-3</v>
       </c>
@@ -7465,6 +8996,9 @@
       <c r="B508" s="5">
         <v>44106</v>
       </c>
+      <c r="C508" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E508" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -7480,6 +9014,9 @@
       <c r="B509" s="5">
         <v>44120</v>
       </c>
+      <c r="C509" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E509" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -7495,6 +9032,9 @@
       <c r="B510" s="5">
         <v>44134</v>
       </c>
+      <c r="C510" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E510" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -7510,6 +9050,9 @@
       <c r="B511" s="5">
         <v>44153</v>
       </c>
+      <c r="C511" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E511" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -7525,6 +9068,9 @@
       <c r="B512" s="5">
         <v>44166</v>
       </c>
+      <c r="C512" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E512" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -7540,6 +9086,9 @@
       <c r="B513" s="5">
         <v>44182</v>
       </c>
+      <c r="C513" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E513" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -7555,6 +9104,9 @@
       <c r="B514" s="5">
         <v>44203</v>
       </c>
+      <c r="C514" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E514" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -7570,6 +9122,9 @@
       <c r="B515" s="5">
         <v>44216</v>
       </c>
+      <c r="C515" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E515" s="3">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -7585,6 +9140,9 @@
       <c r="B516" s="5">
         <v>44230</v>
       </c>
+      <c r="C516" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E516" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -7600,6 +9158,9 @@
       <c r="B517" s="5">
         <v>44250</v>
       </c>
+      <c r="C517" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E517" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -7615,6 +9176,9 @@
       <c r="B518" s="5">
         <v>44257</v>
       </c>
+      <c r="C518" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E518" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -7630,6 +9194,9 @@
       <c r="B519" s="5">
         <v>44272</v>
       </c>
+      <c r="C519" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E519" s="3">
         <v>8.9999999999999993E-3</v>
       </c>
@@ -7645,6 +9212,9 @@
       <c r="B520" s="5">
         <v>44286</v>
       </c>
+      <c r="C520" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E520" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -7660,6 +9230,9 @@
       <c r="B521" s="5">
         <v>44302</v>
       </c>
+      <c r="C521" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E521" s="3">
         <v>1.2999999999999999E-2</v>
       </c>
@@ -7675,6 +9248,9 @@
       <c r="B522" s="5">
         <v>44316</v>
       </c>
+      <c r="C522" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E522" s="3">
         <v>1.6E-2</v>
       </c>
@@ -7690,6 +9266,9 @@
       <c r="B523" s="5">
         <v>44335</v>
       </c>
+      <c r="C523" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E523" s="3">
         <v>1.6E-2</v>
       </c>
@@ -7705,6 +9284,9 @@
       <c r="B524" s="5">
         <v>44348</v>
       </c>
+      <c r="C524" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E524" s="3">
         <v>0.02</v>
       </c>
@@ -7720,6 +9302,9 @@
       <c r="B525" s="5">
         <v>44364</v>
       </c>
+      <c r="C525" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E525" s="3">
         <v>0.02</v>
       </c>
@@ -7735,6 +9320,9 @@
       <c r="B526" s="5">
         <v>44377</v>
       </c>
+      <c r="C526" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E526" s="3">
         <v>1.9E-2</v>
       </c>
@@ -7750,6 +9338,9 @@
       <c r="B527" s="5">
         <v>44393</v>
       </c>
+      <c r="C527" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E527" s="3">
         <v>1.9E-2</v>
       </c>
@@ -7765,6 +9356,9 @@
       <c r="B528" s="5">
         <v>44407</v>
       </c>
+      <c r="C528" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E528" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -7780,6 +9374,9 @@
       <c r="B529" s="5">
         <v>44426</v>
       </c>
+      <c r="C529" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E529" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -7795,6 +9392,9 @@
       <c r="B530" s="5">
         <v>44439</v>
       </c>
+      <c r="C530" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E530" s="3">
         <v>0.03</v>
       </c>
@@ -7810,6 +9410,9 @@
       <c r="B531" s="5">
         <v>44456</v>
       </c>
+      <c r="C531" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E531" s="3">
         <v>0.03</v>
       </c>
@@ -7825,6 +9428,9 @@
       <c r="B532" s="5">
         <v>44470</v>
       </c>
+      <c r="C532" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E532" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
@@ -7840,6 +9446,9 @@
       <c r="B533" s="5">
         <v>44489</v>
       </c>
+      <c r="C533" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E533" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
@@ -7855,6 +9464,9 @@
       <c r="B534" s="5">
         <v>44498</v>
       </c>
+      <c r="C534" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E534" s="3">
         <v>4.1000000000000002E-2</v>
       </c>
@@ -7870,6 +9482,9 @@
       <c r="B535" s="5">
         <v>44517</v>
       </c>
+      <c r="C535" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E535" s="3">
         <v>4.1000000000000002E-2</v>
       </c>
@@ -7885,6 +9500,9 @@
       <c r="B536" s="5">
         <v>44530</v>
       </c>
+      <c r="C536" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E536" s="3">
         <v>4.9000000000000002E-2</v>
       </c>
@@ -7900,6 +9518,9 @@
       <c r="B537" s="5">
         <v>44547</v>
       </c>
+      <c r="C537" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E537" s="3">
         <v>4.9000000000000002E-2</v>
       </c>
@@ -7915,6 +9536,9 @@
       <c r="B538" s="5">
         <v>44568</v>
       </c>
+      <c r="C538" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E538" s="3">
         <v>0.05</v>
       </c>
@@ -7930,6 +9554,9 @@
       <c r="B539" s="5">
         <v>44581</v>
       </c>
+      <c r="C539" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E539" s="3">
         <v>0.05</v>
       </c>
@@ -7945,6 +9572,9 @@
       <c r="B540" s="5">
         <v>44594</v>
       </c>
+      <c r="C540" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E540" s="3">
         <v>5.0999999999999997E-2</v>
       </c>
@@ -7960,6 +9590,9 @@
       <c r="B541" s="5">
         <v>44615</v>
       </c>
+      <c r="C541" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E541" s="3">
         <v>5.0999999999999997E-2</v>
       </c>
@@ -7975,6 +9608,9 @@
       <c r="B542" s="5">
         <v>44622</v>
       </c>
+      <c r="C542" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E542" s="3">
         <v>5.8000000000000003E-2</v>
       </c>
@@ -7990,6 +9626,9 @@
       <c r="B543" s="5">
         <v>44637</v>
       </c>
+      <c r="C543" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E543" s="3">
         <v>5.8999999999999997E-2</v>
       </c>
@@ -8005,6 +9644,9 @@
       <c r="B544" s="5">
         <v>44652</v>
       </c>
+      <c r="C544" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E544" s="3">
         <v>7.4999999999999997E-2</v>
       </c>
@@ -8020,6 +9662,9 @@
       <c r="B545" s="5">
         <v>44672</v>
       </c>
+      <c r="C545" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E545" s="3">
         <v>7.3999999999999996E-2</v>
       </c>
@@ -8035,6 +9680,9 @@
       <c r="B546" s="5">
         <v>44680</v>
       </c>
+      <c r="C546" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E546" s="3">
         <v>7.4999999999999997E-2</v>
       </c>
@@ -8050,6 +9698,9 @@
       <c r="B547" s="5">
         <v>44699</v>
       </c>
+      <c r="C547" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E547" s="3">
         <v>7.3999999999999996E-2</v>
       </c>
@@ -8065,6 +9716,9 @@
       <c r="B548" s="5">
         <v>44712</v>
       </c>
+      <c r="C548" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E548" s="3">
         <v>8.1000000000000003E-2</v>
       </c>
@@ -8080,6 +9734,9 @@
       <c r="B549" s="5">
         <v>44729</v>
       </c>
+      <c r="C549" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E549" s="3">
         <v>8.1000000000000003E-2</v>
       </c>
@@ -8095,6 +9752,9 @@
       <c r="B550" s="5">
         <v>44743</v>
       </c>
+      <c r="C550" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E550" s="3">
         <v>8.5999999999999993E-2</v>
       </c>
@@ -8110,6 +9770,9 @@
       <c r="B551" s="5">
         <v>44761</v>
       </c>
+      <c r="C551" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E551" s="3">
         <v>8.5999999999999993E-2</v>
       </c>
@@ -8125,6 +9788,9 @@
       <c r="B552" s="5">
         <v>44771</v>
       </c>
+      <c r="C552" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E552" s="3">
         <v>8.8999999999999996E-2</v>
       </c>
@@ -8140,6 +9806,9 @@
       <c r="B553" s="5">
         <v>44791</v>
       </c>
+      <c r="C553" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E553" s="3">
         <v>8.8999999999999996E-2</v>
       </c>
@@ -8155,6 +9824,9 @@
       <c r="B554" s="5">
         <v>44804</v>
       </c>
+      <c r="C554" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E554" s="3">
         <v>9.0999999999999998E-2</v>
       </c>
@@ -8170,6 +9842,9 @@
       <c r="B555" s="5">
         <v>44820</v>
       </c>
+      <c r="C555" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E555" s="3">
         <v>9.0999999999999998E-2</v>
       </c>
@@ -8185,6 +9860,9 @@
       <c r="B556" s="5">
         <v>44834</v>
       </c>
+      <c r="C556" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E556" s="3">
         <v>0.1</v>
       </c>
@@ -8200,6 +9878,9 @@
       <c r="B557" s="5">
         <v>44853</v>
       </c>
+      <c r="C557" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E557" s="3">
         <v>9.9000000000000005E-2</v>
       </c>
@@ -8215,6 +9896,9 @@
       <c r="B558" s="5">
         <v>44865</v>
       </c>
+      <c r="C558" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E558" s="3">
         <v>0.107</v>
       </c>
@@ -8230,6 +9914,9 @@
       <c r="B559" s="5">
         <v>44882</v>
       </c>
+      <c r="C559" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E559" s="3">
         <v>0.106</v>
       </c>
@@ -8245,6 +9932,9 @@
       <c r="B560" s="5">
         <v>44895</v>
       </c>
+      <c r="C560" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E560" s="3">
         <v>0.1</v>
       </c>
@@ -8260,6 +9950,9 @@
       <c r="B561" s="5">
         <v>44911</v>
       </c>
+      <c r="C561" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E561" s="3">
         <v>0.10100000000000001</v>
       </c>
@@ -8275,6 +9968,9 @@
       <c r="B562" s="5">
         <v>44932</v>
       </c>
+      <c r="C562" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E562" s="3">
         <v>9.1999999999999998E-2</v>
       </c>
@@ -8290,6 +9986,9 @@
       <c r="B563" s="5">
         <v>44944</v>
       </c>
+      <c r="C563" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E563" s="3">
         <v>9.1999999999999998E-2</v>
       </c>
@@ -8305,6 +10004,9 @@
       <c r="B564" s="5">
         <v>44958</v>
       </c>
+      <c r="C564" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E564" s="3">
         <v>8.5000000000000006E-2</v>
       </c>
@@ -8320,6 +10022,9 @@
       <c r="B565" s="5">
         <v>44980</v>
       </c>
+      <c r="C565" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E565" s="3">
         <v>8.5999999999999993E-2</v>
       </c>
@@ -8335,6 +10040,9 @@
       <c r="B566" s="5">
         <v>44987</v>
       </c>
+      <c r="C566" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E566" s="3">
         <v>8.5000000000000006E-2</v>
       </c>
@@ -8350,6 +10058,9 @@
       <c r="B567" s="5">
         <v>45002</v>
       </c>
+      <c r="C567" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E567" s="3">
         <v>8.5000000000000006E-2</v>
       </c>
@@ -8365,6 +10076,9 @@
       <c r="B568" s="5">
         <v>45016</v>
       </c>
+      <c r="C568" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E568" s="3">
         <v>6.9000000000000006E-2</v>
       </c>
@@ -8380,6 +10094,9 @@
       <c r="B569" s="5">
         <v>45035</v>
       </c>
+      <c r="C569" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E569" s="3">
         <v>6.9000000000000006E-2</v>
       </c>
@@ -8395,6 +10112,9 @@
       <c r="B570" s="5">
         <v>45048</v>
       </c>
+      <c r="C570" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E570" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -8410,6 +10130,9 @@
       <c r="B571" s="5">
         <v>45063</v>
       </c>
+      <c r="C571" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E571" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -8425,6 +10148,9 @@
       <c r="B572" s="5">
         <v>45078</v>
       </c>
+      <c r="C572" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E572" s="3">
         <v>6.0999999999999999E-2</v>
       </c>
@@ -8440,6 +10166,9 @@
       <c r="B573" s="5">
         <v>45093</v>
       </c>
+      <c r="C573" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E573" s="3">
         <v>6.0999999999999999E-2</v>
       </c>
@@ -8455,6 +10184,9 @@
       <c r="B574" s="5">
         <v>45107</v>
       </c>
+      <c r="C574" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E574" s="3">
         <v>5.5E-2</v>
       </c>
@@ -8470,6 +10202,9 @@
       <c r="B575" s="5">
         <v>45126</v>
       </c>
+      <c r="C575" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E575" s="3">
         <v>5.5E-2</v>
       </c>
@@ -8485,6 +10220,9 @@
       <c r="B576" s="5">
         <v>45138</v>
       </c>
+      <c r="C576" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E576" s="3">
         <v>5.2999999999999999E-2</v>
       </c>
@@ -8500,6 +10238,9 @@
       <c r="B577" s="5">
         <v>45156</v>
       </c>
+      <c r="C577" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E577" s="3">
         <v>5.2999999999999999E-2</v>
       </c>
@@ -8515,6 +10256,9 @@
       <c r="B578" s="5">
         <v>45169</v>
       </c>
+      <c r="C578" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E578" s="3">
         <v>5.2999999999999999E-2</v>
       </c>
@@ -8530,6 +10274,9 @@
       <c r="B579" s="5">
         <v>45188</v>
       </c>
+      <c r="C579" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E579" s="3">
         <v>5.1999999999999998E-2</v>
       </c>
@@ -8545,6 +10292,9 @@
       <c r="B580" s="5">
         <v>45198</v>
       </c>
+      <c r="C580" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E580" s="3">
         <v>4.2999999999999997E-2</v>
       </c>
@@ -8560,6 +10310,9 @@
       <c r="B581" s="5">
         <v>45217</v>
       </c>
+      <c r="C581" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E581" s="3">
         <v>4.2999999999999997E-2</v>
       </c>
@@ -8575,6 +10328,9 @@
       <c r="B582" s="5">
         <v>45230</v>
       </c>
+      <c r="C582" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E582" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -8590,6 +10346,9 @@
       <c r="B583" s="5">
         <v>45247</v>
       </c>
+      <c r="C583" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E583" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -8605,6 +10364,9 @@
       <c r="B584" s="5">
         <v>45260</v>
       </c>
+      <c r="C584" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E584" s="3">
         <v>2.4E-2</v>
       </c>
@@ -8620,6 +10382,9 @@
       <c r="B585" s="5">
         <v>45279</v>
       </c>
+      <c r="C585" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E585" s="3">
         <v>2.4E-2</v>
       </c>
@@ -8635,6 +10400,9 @@
       <c r="B586" s="5">
         <v>45296</v>
       </c>
+      <c r="C586" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E586" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -8650,6 +10418,9 @@
       <c r="B587" s="5">
         <v>45308</v>
       </c>
+      <c r="C587" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E587" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -8665,6 +10436,9 @@
       <c r="B588" s="5">
         <v>45323</v>
       </c>
+      <c r="C588" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E588" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -8680,6 +10454,9 @@
       <c r="B589" s="5">
         <v>45344</v>
       </c>
+      <c r="C589" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E589" s="3">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -8695,6 +10472,9 @@
       <c r="B590" s="5">
         <v>45352</v>
       </c>
+      <c r="C590" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E590" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -8710,6 +10490,9 @@
       <c r="B591" s="5">
         <v>45369</v>
       </c>
+      <c r="C591" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E591" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -8725,6 +10508,9 @@
       <c r="B592" s="5">
         <v>45385</v>
       </c>
+      <c r="C592" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E592" s="3">
         <v>2.4E-2</v>
       </c>
@@ -8740,6 +10526,9 @@
       <c r="B593" s="5">
         <v>45399</v>
       </c>
+      <c r="C593" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E593" s="3">
         <v>2.4E-2</v>
       </c>
@@ -8755,6 +10544,9 @@
       <c r="B594" s="5">
         <v>45412</v>
       </c>
+      <c r="C594" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E594" s="3">
         <v>2.4E-2</v>
       </c>
@@ -8770,6 +10562,9 @@
       <c r="B595" s="5">
         <v>45429</v>
       </c>
+      <c r="C595" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E595" s="3">
         <v>2.4E-2</v>
       </c>
@@ -8785,6 +10580,9 @@
       <c r="B596" s="5">
         <v>45443</v>
       </c>
+      <c r="C596" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E596" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -8800,6 +10598,9 @@
       <c r="B597" s="5">
         <v>45461</v>
       </c>
+      <c r="C597" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E597" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -8815,6 +10616,9 @@
       <c r="B598" s="5">
         <v>45475</v>
       </c>
+      <c r="C598" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E598" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -8830,6 +10634,9 @@
       <c r="B599" s="5">
         <v>45490</v>
       </c>
+      <c r="C599" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E599" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -8845,6 +10652,9 @@
       <c r="B600" s="5">
         <v>45504</v>
       </c>
+      <c r="C600" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E600" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -8860,6 +10670,9 @@
       <c r="B601" s="5">
         <v>45524</v>
       </c>
+      <c r="C601" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E601" s="3">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -8875,6 +10688,9 @@
       <c r="B602" s="5">
         <v>45534</v>
       </c>
+      <c r="C602" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E602" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -8890,6 +10706,9 @@
       <c r="B603" s="5">
         <v>45553</v>
       </c>
+      <c r="C603" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E603" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -8905,6 +10724,9 @@
       <c r="B604" s="5">
         <v>45566</v>
       </c>
+      <c r="C604" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E604" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
@@ -8920,6 +10742,9 @@
       <c r="B605" s="5">
         <v>45582</v>
       </c>
+      <c r="C605" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E605" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -8935,6 +10760,9 @@
       <c r="B606" s="5">
         <v>45596</v>
       </c>
+      <c r="C606" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E606" s="3">
         <v>0.02</v>
       </c>
@@ -8950,6 +10778,9 @@
       <c r="B607" s="5">
         <v>45615</v>
       </c>
+      <c r="C607" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E607" s="3">
         <v>0.02</v>
       </c>
@@ -8965,6 +10796,9 @@
       <c r="B608" s="5">
         <v>45625</v>
       </c>
+      <c r="C608" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E608" s="3">
         <v>2.3E-2</v>
       </c>
@@ -8980,6 +10814,9 @@
       <c r="B609" s="5">
         <v>45644</v>
       </c>
+      <c r="C609" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E609" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -8995,6 +10832,9 @@
       <c r="B610" s="5">
         <v>45664</v>
       </c>
+      <c r="C610" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E610" s="3">
         <v>2.4E-2</v>
       </c>
@@ -9010,6 +10850,9 @@
       <c r="B611" s="5">
         <v>45674</v>
       </c>
+      <c r="C611" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E611" s="3">
         <v>2.4E-2</v>
       </c>
@@ -9025,6 +10868,9 @@
       <c r="B612" s="5">
         <v>45691</v>
       </c>
+      <c r="C612" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E612" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -9040,6 +10886,9 @@
       <c r="B613" s="5">
         <v>45712</v>
       </c>
+      <c r="C613" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E613" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -9055,6 +10904,9 @@
       <c r="B614" s="5">
         <v>45719</v>
       </c>
+      <c r="C614" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E614" s="3">
         <v>2.4E-2</v>
       </c>
@@ -9070,6 +10922,9 @@
       <c r="B615" s="5">
         <v>45735</v>
       </c>
+      <c r="C615" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E615" s="3">
         <v>2.3E-2</v>
       </c>
@@ -9085,6 +10940,9 @@
       <c r="B616" s="5">
         <v>45748</v>
       </c>
+      <c r="C616" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E616" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -9100,6 +10958,9 @@
       <c r="B617" s="5">
         <v>45763</v>
       </c>
+      <c r="C617" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E617" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -9115,6 +10976,9 @@
       <c r="B618" s="5">
         <v>45779</v>
       </c>
+      <c r="C618" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E618" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -9130,6 +10994,9 @@
       <c r="B619" s="5">
         <v>45796</v>
       </c>
+      <c r="C619" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E619" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -9145,6 +11012,9 @@
       <c r="B620" s="5">
         <v>45811</v>
       </c>
+      <c r="C620" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E620" s="3">
         <v>1.9E-2</v>
       </c>
@@ -9160,6 +11030,9 @@
       <c r="B621" s="5">
         <v>45826</v>
       </c>
+      <c r="C621" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E621" s="3">
         <v>1.9E-2</v>
       </c>
@@ -9175,6 +11048,9 @@
       <c r="B622" s="5">
         <v>45839</v>
       </c>
+      <c r="C622" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E622" s="3">
         <v>0.02</v>
       </c>
@@ -9190,6 +11066,9 @@
       <c r="B623" s="5">
         <v>45855</v>
       </c>
+      <c r="C623" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E623" s="3">
         <v>0.02</v>
       </c>
@@ -9205,6 +11084,9 @@
       <c r="B624" s="5">
         <v>45870</v>
       </c>
+      <c r="C624" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E624" s="3">
         <v>0.02</v>
       </c>
@@ -9215,11 +11097,14 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A625" s="6"/>
       <c r="B625" s="5">
         <v>45889</v>
       </c>
+      <c r="C625" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E625" s="3">
         <v>0.02</v>
       </c>
@@ -9230,11 +11115,16 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A626" s="6"/>
+    <row r="626" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A626" s="6">
+        <v>45870</v>
+      </c>
       <c r="B626" s="5">
         <v>45902</v>
       </c>
+      <c r="C626" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E626" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -9244,12 +11134,20 @@
       <c r="G626" s="3">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A627" s="6"/>
+      <c r="H626" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A627" s="6">
+        <v>45870</v>
+      </c>
       <c r="B627" s="5">
         <v>45917</v>
       </c>
+      <c r="C627" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E627" s="3">
         <v>0.02</v>
       </c>
@@ -9260,11 +11158,16 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A628" s="6"/>
+    <row r="628" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A628" s="6">
+        <v>45901</v>
+      </c>
       <c r="B628" s="5">
         <v>45931</v>
       </c>
+      <c r="C628" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E628" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -9274,12 +11177,20 @@
       <c r="G628" s="3">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A629" s="6"/>
+      <c r="H628" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A629" s="6">
+        <v>45901</v>
+      </c>
       <c r="B629" s="5">
         <v>45947</v>
       </c>
+      <c r="C629" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E629" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -9290,11 +11201,16 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A630" s="6"/>
+    <row r="630" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A630" s="6">
+        <v>45931</v>
+      </c>
       <c r="B630" s="5">
         <v>45961</v>
       </c>
+      <c r="C630" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E630" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -9304,12 +11220,20 @@
       <c r="G630" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
-    </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A631" s="6"/>
+      <c r="H630" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A631" s="6">
+        <v>45931</v>
+      </c>
       <c r="B631" s="5">
         <v>45980</v>
       </c>
+      <c r="C631" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E631" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -9320,11 +11244,16 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A632" s="6"/>
+    <row r="632" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A632" s="6">
+        <v>45962</v>
+      </c>
       <c r="B632" s="5">
         <v>45993</v>
       </c>
+      <c r="C632" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E632" s="3">
         <v>2.1999999999999999E-2</v>
       </c>
@@ -9334,11 +11263,20 @@
       <c r="G632" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
-    </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H632" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A633" s="6">
+        <v>45962</v>
+      </c>
       <c r="B633" s="5">
         <v>46008</v>
       </c>
+      <c r="C633" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E633" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
@@ -9349,10 +11287,16 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A634" s="6">
+        <v>45992</v>
+      </c>
       <c r="B634" s="5">
         <v>46029</v>
       </c>
+      <c r="C634" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E634" s="3">
         <v>0.02</v>
       </c>
@@ -9362,11 +11306,20 @@
       <c r="G634" s="3">
         <v>2.1000000000000001E-2</v>
       </c>
-    </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H634" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A635" s="6">
+        <v>45992</v>
+      </c>
       <c r="B635" s="5">
         <v>46041</v>
       </c>
+      <c r="C635" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E635" s="3">
         <v>1.9E-2</v>
       </c>
@@ -9377,10 +11330,16 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A636" s="6">
+        <v>46023</v>
+      </c>
       <c r="B636" s="5">
         <v>46057</v>
       </c>
+      <c r="C636" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E636" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -9390,11 +11349,20 @@
       <c r="G636" s="3">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H636" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="637" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A637" s="6">
+        <v>46023</v>
+      </c>
       <c r="B637" s="5">
         <v>46078</v>
       </c>
+      <c r="C637" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E637" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -9405,10 +11373,16 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A638" s="6">
+        <v>46054</v>
+      </c>
       <c r="B638" s="5">
         <v>46084</v>
       </c>
+      <c r="C638" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E638" s="3">
         <v>1.9E-2</v>
       </c>
@@ -9418,11 +11392,20 @@
       <c r="G638" s="3">
         <v>1.7000000000000001E-2</v>
       </c>
-    </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H638" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A639" s="6">
+        <v>46054</v>
+      </c>
       <c r="B639" s="5">
         <v>46099</v>
       </c>
+      <c r="C639" s="14">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="E639" s="3">
         <v>1.9E-2</v>
       </c>
@@ -9433,12 +11416,70 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A640" s="6">
+        <v>46082</v>
+      </c>
       <c r="B640" s="5">
         <v>46112</v>
       </c>
+      <c r="C640" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E640" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F640" s="3">
+        <v>2.5999999999999999E-2</v>
+      </c>
       <c r="G640" s="3">
         <v>1.9E-2</v>
+      </c>
+      <c r="H640" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A641" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B641" s="5">
+        <v>46128</v>
+      </c>
+      <c r="C641" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E641" s="3">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="F641" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G641" s="3">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="642" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A642" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B642" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C642" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E642" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="F642" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="G642" s="3">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="H642" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9450,7 +11491,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D09B9D-81F6-404C-864F-A035EBA561C3}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="2"/>
   </cols>
